--- a/output/version3/test/20-15/MARL/IL/RL-RL/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-15/MARL/IL/RL-RL/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1019</v>
+        <v>959</v>
       </c>
       <c r="C2" t="n">
-        <v>956</v>
+        <v>845</v>
       </c>
       <c r="D2" t="n">
-        <v>1005</v>
+        <v>819</v>
       </c>
       <c r="E2" t="n">
-        <v>795</v>
+        <v>975</v>
       </c>
       <c r="F2" t="n">
-        <v>832</v>
+        <v>861</v>
       </c>
       <c r="G2" t="n">
-        <v>943</v>
+        <v>1022</v>
       </c>
       <c r="H2" t="n">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="I2" t="n">
-        <v>893</v>
+        <v>975</v>
       </c>
       <c r="J2" t="n">
-        <v>876</v>
+        <v>830</v>
       </c>
       <c r="K2" t="n">
-        <v>958</v>
+        <v>1020</v>
       </c>
       <c r="L2" t="n">
-        <v>917</v>
+        <v>919.4</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
+        <v>976</v>
+      </c>
+      <c r="C3" t="n">
+        <v>963</v>
+      </c>
+      <c r="D3" t="n">
+        <v>875</v>
+      </c>
+      <c r="E3" t="n">
+        <v>939</v>
+      </c>
+      <c r="F3" t="n">
         <v>1046</v>
       </c>
-      <c r="C3" t="n">
-        <v>890</v>
-      </c>
-      <c r="D3" t="n">
-        <v>890</v>
-      </c>
-      <c r="E3" t="n">
-        <v>948</v>
-      </c>
-      <c r="F3" t="n">
-        <v>861</v>
-      </c>
       <c r="G3" t="n">
-        <v>991</v>
+        <v>939</v>
       </c>
       <c r="H3" t="n">
-        <v>925</v>
+        <v>1001</v>
       </c>
       <c r="I3" t="n">
-        <v>978</v>
+        <v>907</v>
       </c>
       <c r="J3" t="n">
-        <v>872</v>
+        <v>965</v>
       </c>
       <c r="K3" t="n">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="L3" t="n">
-        <v>945.4</v>
+        <v>967.2</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>967</v>
+        <v>917</v>
       </c>
       <c r="C4" t="n">
-        <v>1080</v>
+        <v>882</v>
       </c>
       <c r="D4" t="n">
-        <v>796</v>
+        <v>1117</v>
       </c>
       <c r="E4" t="n">
-        <v>871</v>
+        <v>817</v>
       </c>
       <c r="F4" t="n">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="G4" t="n">
-        <v>773</v>
+        <v>1042</v>
       </c>
       <c r="H4" t="n">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="I4" t="n">
-        <v>800</v>
+        <v>718</v>
       </c>
       <c r="J4" t="n">
-        <v>721</v>
+        <v>879</v>
       </c>
       <c r="K4" t="n">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="L4" t="n">
-        <v>864.5</v>
+        <v>901.1</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>939</v>
+        <v>922</v>
       </c>
       <c r="C5" t="n">
-        <v>768</v>
+        <v>894</v>
       </c>
       <c r="D5" t="n">
-        <v>1089</v>
+        <v>848</v>
       </c>
       <c r="E5" t="n">
-        <v>853</v>
+        <v>734</v>
       </c>
       <c r="F5" t="n">
-        <v>884</v>
+        <v>797</v>
       </c>
       <c r="G5" t="n">
-        <v>937</v>
+        <v>797</v>
       </c>
       <c r="H5" t="n">
-        <v>992</v>
+        <v>766</v>
       </c>
       <c r="I5" t="n">
-        <v>845</v>
+        <v>903</v>
       </c>
       <c r="J5" t="n">
-        <v>773</v>
+        <v>991</v>
       </c>
       <c r="K5" t="n">
-        <v>802</v>
+        <v>982</v>
       </c>
       <c r="L5" t="n">
-        <v>888.2</v>
+        <v>863.4</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>713</v>
+        <v>792</v>
       </c>
       <c r="C6" t="n">
-        <v>712</v>
+        <v>664</v>
       </c>
       <c r="D6" t="n">
-        <v>774</v>
+        <v>737</v>
       </c>
       <c r="E6" t="n">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="F6" t="n">
-        <v>729</v>
+        <v>760</v>
       </c>
       <c r="G6" t="n">
-        <v>704</v>
+        <v>832</v>
       </c>
       <c r="H6" t="n">
-        <v>784</v>
+        <v>706</v>
       </c>
       <c r="I6" t="n">
-        <v>737</v>
+        <v>824</v>
       </c>
       <c r="J6" t="n">
-        <v>742</v>
+        <v>882</v>
       </c>
       <c r="K6" t="n">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="L6" t="n">
-        <v>735.5</v>
+        <v>764.9</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>928</v>
+        <v>861</v>
       </c>
       <c r="C7" t="n">
-        <v>899</v>
+        <v>798</v>
       </c>
       <c r="D7" t="n">
-        <v>825</v>
+        <v>768</v>
       </c>
       <c r="E7" t="n">
-        <v>1095</v>
+        <v>871</v>
       </c>
       <c r="F7" t="n">
-        <v>871</v>
+        <v>963</v>
       </c>
       <c r="G7" t="n">
-        <v>894</v>
+        <v>934</v>
       </c>
       <c r="H7" t="n">
-        <v>996</v>
+        <v>851</v>
       </c>
       <c r="I7" t="n">
-        <v>935</v>
+        <v>882</v>
       </c>
       <c r="J7" t="n">
-        <v>973</v>
+        <v>876</v>
       </c>
       <c r="K7" t="n">
-        <v>995</v>
+        <v>791</v>
       </c>
       <c r="L7" t="n">
-        <v>941.1</v>
+        <v>859.5</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>977</v>
+        <v>925</v>
       </c>
       <c r="C8" t="n">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="D8" t="n">
-        <v>1017</v>
+        <v>786</v>
       </c>
       <c r="E8" t="n">
-        <v>881</v>
+        <v>870</v>
       </c>
       <c r="F8" t="n">
-        <v>1116</v>
+        <v>896</v>
       </c>
       <c r="G8" t="n">
-        <v>909</v>
+        <v>853</v>
       </c>
       <c r="H8" t="n">
-        <v>1045</v>
+        <v>997</v>
       </c>
       <c r="I8" t="n">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="J8" t="n">
-        <v>812</v>
+        <v>1080</v>
       </c>
       <c r="K8" t="n">
-        <v>919</v>
+        <v>1083</v>
       </c>
       <c r="L8" t="n">
-        <v>958</v>
+        <v>938.5</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>902</v>
+        <v>933</v>
       </c>
       <c r="C9" t="n">
-        <v>1028</v>
+        <v>997</v>
       </c>
       <c r="D9" t="n">
-        <v>850</v>
+        <v>783</v>
       </c>
       <c r="E9" t="n">
-        <v>891</v>
+        <v>820</v>
       </c>
       <c r="F9" t="n">
-        <v>899</v>
+        <v>915</v>
       </c>
       <c r="G9" t="n">
-        <v>854</v>
+        <v>846</v>
       </c>
       <c r="H9" t="n">
-        <v>779</v>
+        <v>857</v>
       </c>
       <c r="I9" t="n">
-        <v>753</v>
+        <v>809</v>
       </c>
       <c r="J9" t="n">
-        <v>706</v>
+        <v>844</v>
       </c>
       <c r="K9" t="n">
-        <v>1026</v>
+        <v>980</v>
       </c>
       <c r="L9" t="n">
-        <v>868.8</v>
+        <v>878.4</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>820</v>
+        <v>939</v>
       </c>
       <c r="C10" t="n">
-        <v>835</v>
+        <v>896</v>
       </c>
       <c r="D10" t="n">
-        <v>1096</v>
+        <v>823</v>
       </c>
       <c r="E10" t="n">
-        <v>905</v>
+        <v>780</v>
       </c>
       <c r="F10" t="n">
-        <v>1026</v>
+        <v>705</v>
       </c>
       <c r="G10" t="n">
-        <v>912</v>
+        <v>873</v>
       </c>
       <c r="H10" t="n">
-        <v>1079</v>
+        <v>862</v>
       </c>
       <c r="I10" t="n">
-        <v>893</v>
+        <v>867</v>
       </c>
       <c r="J10" t="n">
-        <v>967</v>
+        <v>883</v>
       </c>
       <c r="K10" t="n">
-        <v>1024</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>955.7</v>
+        <v>857.8</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>866</v>
+        <v>980</v>
       </c>
       <c r="C11" t="n">
-        <v>890</v>
+        <v>962</v>
       </c>
       <c r="D11" t="n">
-        <v>763</v>
+        <v>972</v>
       </c>
       <c r="E11" t="n">
-        <v>861</v>
+        <v>958</v>
       </c>
       <c r="F11" t="n">
+        <v>1004</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1048</v>
+      </c>
+      <c r="H11" t="n">
+        <v>900</v>
+      </c>
+      <c r="I11" t="n">
         <v>990</v>
       </c>
-      <c r="G11" t="n">
-        <v>820</v>
-      </c>
-      <c r="H11" t="n">
-        <v>933</v>
-      </c>
-      <c r="I11" t="n">
-        <v>810</v>
-      </c>
       <c r="J11" t="n">
-        <v>808</v>
+        <v>991</v>
       </c>
       <c r="K11" t="n">
-        <v>970</v>
+        <v>907</v>
       </c>
       <c r="L11" t="n">
-        <v>871.1</v>
+        <v>971.2</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>871</v>
+        <v>1085</v>
       </c>
       <c r="C12" t="n">
-        <v>1145</v>
+        <v>991</v>
       </c>
       <c r="D12" t="n">
-        <v>935</v>
+        <v>1012</v>
       </c>
       <c r="E12" t="n">
-        <v>856</v>
+        <v>1099</v>
       </c>
       <c r="F12" t="n">
-        <v>1039</v>
+        <v>970</v>
       </c>
       <c r="G12" t="n">
-        <v>1124</v>
+        <v>907</v>
       </c>
       <c r="H12" t="n">
-        <v>936</v>
+        <v>839</v>
       </c>
       <c r="I12" t="n">
-        <v>1197</v>
+        <v>1063</v>
       </c>
       <c r="J12" t="n">
-        <v>1049</v>
+        <v>1077</v>
       </c>
       <c r="K12" t="n">
-        <v>1093</v>
+        <v>1053</v>
       </c>
       <c r="L12" t="n">
-        <v>1024.5</v>
+        <v>1009.6</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>882</v>
+        <v>854</v>
       </c>
       <c r="C13" t="n">
-        <v>900</v>
+        <v>733</v>
       </c>
       <c r="D13" t="n">
-        <v>967</v>
+        <v>945</v>
       </c>
       <c r="E13" t="n">
-        <v>970</v>
+        <v>856</v>
       </c>
       <c r="F13" t="n">
-        <v>797</v>
+        <v>759</v>
       </c>
       <c r="G13" t="n">
-        <v>708</v>
+        <v>768</v>
       </c>
       <c r="H13" t="n">
-        <v>989</v>
+        <v>798</v>
       </c>
       <c r="I13" t="n">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="J13" t="n">
-        <v>855</v>
+        <v>930</v>
       </c>
       <c r="K13" t="n">
-        <v>771</v>
+        <v>805</v>
       </c>
       <c r="L13" t="n">
-        <v>857.8</v>
+        <v>818.1</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>994</v>
+        <v>803</v>
       </c>
       <c r="C14" t="n">
-        <v>732</v>
+        <v>987</v>
       </c>
       <c r="D14" t="n">
-        <v>800</v>
+        <v>892</v>
       </c>
       <c r="E14" t="n">
-        <v>851</v>
+        <v>998</v>
       </c>
       <c r="F14" t="n">
-        <v>941</v>
+        <v>810</v>
       </c>
       <c r="G14" t="n">
-        <v>976</v>
+        <v>962</v>
       </c>
       <c r="H14" t="n">
-        <v>958</v>
+        <v>924</v>
       </c>
       <c r="I14" t="n">
-        <v>803</v>
+        <v>923</v>
       </c>
       <c r="J14" t="n">
-        <v>851</v>
+        <v>1012</v>
       </c>
       <c r="K14" t="n">
-        <v>868</v>
+        <v>946</v>
       </c>
       <c r="L14" t="n">
-        <v>877.4</v>
+        <v>925.7</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>858</v>
+        <v>825</v>
       </c>
       <c r="C15" t="n">
-        <v>1060</v>
+        <v>847</v>
       </c>
       <c r="D15" t="n">
-        <v>794</v>
+        <v>1207</v>
       </c>
       <c r="E15" t="n">
-        <v>887</v>
+        <v>951</v>
       </c>
       <c r="F15" t="n">
-        <v>898</v>
+        <v>840</v>
       </c>
       <c r="G15" t="n">
-        <v>815</v>
+        <v>1064</v>
       </c>
       <c r="H15" t="n">
-        <v>973</v>
+        <v>875</v>
       </c>
       <c r="I15" t="n">
-        <v>828</v>
+        <v>1101</v>
       </c>
       <c r="J15" t="n">
-        <v>805</v>
+        <v>788</v>
       </c>
       <c r="K15" t="n">
-        <v>969</v>
+        <v>948</v>
       </c>
       <c r="L15" t="n">
-        <v>888.7</v>
+        <v>944.6</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>1024</v>
+        <v>940</v>
       </c>
       <c r="C16" t="n">
-        <v>906</v>
+        <v>911</v>
       </c>
       <c r="D16" t="n">
-        <v>1023</v>
+        <v>933</v>
       </c>
       <c r="E16" t="n">
-        <v>839</v>
+        <v>787</v>
       </c>
       <c r="F16" t="n">
-        <v>963</v>
+        <v>872</v>
       </c>
       <c r="G16" t="n">
-        <v>911</v>
+        <v>889</v>
       </c>
       <c r="H16" t="n">
-        <v>826</v>
+        <v>975</v>
       </c>
       <c r="I16" t="n">
-        <v>929</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>914</v>
+        <v>966</v>
       </c>
       <c r="K16" t="n">
-        <v>1149</v>
+        <v>875</v>
       </c>
       <c r="L16" t="n">
-        <v>948.4</v>
+        <v>914.8</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1022</v>
+        <v>811</v>
       </c>
       <c r="C17" t="n">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="D17" t="n">
-        <v>811</v>
+        <v>982</v>
       </c>
       <c r="E17" t="n">
-        <v>1011</v>
+        <v>997</v>
       </c>
       <c r="F17" t="n">
-        <v>925</v>
+        <v>897</v>
       </c>
       <c r="G17" t="n">
-        <v>944</v>
+        <v>985</v>
       </c>
       <c r="H17" t="n">
-        <v>810</v>
+        <v>871</v>
       </c>
       <c r="I17" t="n">
-        <v>1016</v>
+        <v>793</v>
       </c>
       <c r="J17" t="n">
-        <v>916</v>
+        <v>835</v>
       </c>
       <c r="K17" t="n">
-        <v>817</v>
+        <v>759</v>
       </c>
       <c r="L17" t="n">
-        <v>918.1</v>
+        <v>883.3</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>910</v>
+        <v>1035</v>
       </c>
       <c r="C18" t="n">
+        <v>950</v>
+      </c>
+      <c r="D18" t="n">
+        <v>977</v>
+      </c>
+      <c r="E18" t="n">
+        <v>894</v>
+      </c>
+      <c r="F18" t="n">
+        <v>894</v>
+      </c>
+      <c r="G18" t="n">
         <v>918</v>
       </c>
-      <c r="D18" t="n">
-        <v>973</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1069</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1012</v>
-      </c>
-      <c r="G18" t="n">
-        <v>974</v>
-      </c>
       <c r="H18" t="n">
-        <v>863</v>
+        <v>877</v>
       </c>
       <c r="I18" t="n">
-        <v>858</v>
+        <v>933</v>
       </c>
       <c r="J18" t="n">
-        <v>942</v>
+        <v>888</v>
       </c>
       <c r="K18" t="n">
-        <v>890</v>
+        <v>966</v>
       </c>
       <c r="L18" t="n">
-        <v>940.9</v>
+        <v>933.2</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>922</v>
+        <v>803</v>
       </c>
       <c r="C19" t="n">
-        <v>958</v>
+        <v>773</v>
       </c>
       <c r="D19" t="n">
-        <v>729</v>
+        <v>820</v>
       </c>
       <c r="E19" t="n">
-        <v>797</v>
+        <v>824</v>
       </c>
       <c r="F19" t="n">
-        <v>1053</v>
+        <v>777</v>
       </c>
       <c r="G19" t="n">
-        <v>1003</v>
+        <v>918</v>
       </c>
       <c r="H19" t="n">
-        <v>911</v>
+        <v>967</v>
       </c>
       <c r="I19" t="n">
-        <v>892</v>
+        <v>1002</v>
       </c>
       <c r="J19" t="n">
-        <v>753</v>
+        <v>859</v>
       </c>
       <c r="K19" t="n">
-        <v>779</v>
+        <v>929</v>
       </c>
       <c r="L19" t="n">
-        <v>879.7</v>
+        <v>867.2</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>966</v>
+        <v>902</v>
       </c>
       <c r="C20" t="n">
-        <v>866</v>
+        <v>936</v>
       </c>
       <c r="D20" t="n">
-        <v>966</v>
+        <v>769</v>
       </c>
       <c r="E20" t="n">
-        <v>1110</v>
+        <v>975</v>
       </c>
       <c r="F20" t="n">
-        <v>910</v>
+        <v>945</v>
       </c>
       <c r="G20" t="n">
-        <v>989</v>
+        <v>840</v>
       </c>
       <c r="H20" t="n">
-        <v>1027</v>
+        <v>924</v>
       </c>
       <c r="I20" t="n">
-        <v>868</v>
+        <v>979</v>
       </c>
       <c r="J20" t="n">
-        <v>1022</v>
+        <v>1069</v>
       </c>
       <c r="K20" t="n">
-        <v>1080</v>
+        <v>997</v>
       </c>
       <c r="L20" t="n">
-        <v>980.4</v>
+        <v>933.6</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>857</v>
+        <v>776</v>
       </c>
       <c r="C21" t="n">
-        <v>826</v>
+        <v>991</v>
       </c>
       <c r="D21" t="n">
-        <v>859</v>
+        <v>960</v>
       </c>
       <c r="E21" t="n">
-        <v>851</v>
+        <v>907</v>
       </c>
       <c r="F21" t="n">
-        <v>1006</v>
+        <v>853</v>
       </c>
       <c r="G21" t="n">
-        <v>847</v>
+        <v>997</v>
       </c>
       <c r="H21" t="n">
-        <v>970</v>
+        <v>958</v>
       </c>
       <c r="I21" t="n">
-        <v>997</v>
+        <v>1051</v>
       </c>
       <c r="J21" t="n">
-        <v>959</v>
+        <v>771</v>
       </c>
       <c r="K21" t="n">
-        <v>1008</v>
+        <v>1051</v>
       </c>
       <c r="L21" t="n">
-        <v>918</v>
+        <v>931.5</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>862</v>
+        <v>931</v>
       </c>
       <c r="C22" t="n">
-        <v>966</v>
+        <v>851</v>
       </c>
       <c r="D22" t="n">
-        <v>800</v>
+        <v>1029</v>
       </c>
       <c r="E22" t="n">
-        <v>841</v>
+        <v>1013</v>
       </c>
       <c r="F22" t="n">
-        <v>864</v>
+        <v>817</v>
       </c>
       <c r="G22" t="n">
-        <v>861</v>
+        <v>945</v>
       </c>
       <c r="H22" t="n">
-        <v>1047</v>
+        <v>794</v>
       </c>
       <c r="I22" t="n">
-        <v>910</v>
+        <v>954</v>
       </c>
       <c r="J22" t="n">
-        <v>840</v>
+        <v>934</v>
       </c>
       <c r="K22" t="n">
-        <v>1014</v>
+        <v>824</v>
       </c>
       <c r="L22" t="n">
-        <v>900.5</v>
+        <v>909.2</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>964</v>
+        <v>1016</v>
       </c>
       <c r="C23" t="n">
-        <v>979</v>
+        <v>1053</v>
       </c>
       <c r="D23" t="n">
-        <v>1113</v>
+        <v>953</v>
       </c>
       <c r="E23" t="n">
-        <v>944</v>
+        <v>1122</v>
       </c>
       <c r="F23" t="n">
-        <v>1000</v>
+        <v>1014</v>
       </c>
       <c r="G23" t="n">
-        <v>1035</v>
+        <v>1123</v>
       </c>
       <c r="H23" t="n">
-        <v>1072</v>
+        <v>928</v>
       </c>
       <c r="I23" t="n">
-        <v>1128</v>
+        <v>1005</v>
       </c>
       <c r="J23" t="n">
-        <v>1006</v>
+        <v>1081</v>
       </c>
       <c r="K23" t="n">
-        <v>1012</v>
+        <v>1115</v>
       </c>
       <c r="L23" t="n">
-        <v>1025.3</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>956</v>
+        <v>1069</v>
       </c>
       <c r="C24" t="n">
-        <v>1014</v>
+        <v>1030</v>
       </c>
       <c r="D24" t="n">
-        <v>924</v>
+        <v>1170</v>
       </c>
       <c r="E24" t="n">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F24" t="n">
-        <v>939</v>
+        <v>964</v>
       </c>
       <c r="G24" t="n">
-        <v>950</v>
+        <v>1143</v>
       </c>
       <c r="H24" t="n">
-        <v>1064</v>
+        <v>968</v>
       </c>
       <c r="I24" t="n">
-        <v>1109</v>
+        <v>881</v>
       </c>
       <c r="J24" t="n">
-        <v>1092</v>
+        <v>1026</v>
       </c>
       <c r="K24" t="n">
-        <v>1007</v>
+        <v>933</v>
       </c>
       <c r="L24" t="n">
-        <v>1013.9</v>
+        <v>1026.9</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>895</v>
+        <v>878</v>
       </c>
       <c r="C25" t="n">
-        <v>898</v>
+        <v>1027</v>
       </c>
       <c r="D25" t="n">
-        <v>958</v>
+        <v>984</v>
       </c>
       <c r="E25" t="n">
-        <v>941</v>
+        <v>909</v>
       </c>
       <c r="F25" t="n">
-        <v>841</v>
+        <v>855</v>
       </c>
       <c r="G25" t="n">
-        <v>824</v>
+        <v>847</v>
       </c>
       <c r="H25" t="n">
-        <v>861</v>
+        <v>953</v>
       </c>
       <c r="I25" t="n">
-        <v>1040</v>
+        <v>811</v>
       </c>
       <c r="J25" t="n">
-        <v>1099</v>
+        <v>1210</v>
       </c>
       <c r="K25" t="n">
-        <v>1027</v>
+        <v>889</v>
       </c>
       <c r="L25" t="n">
-        <v>938.4</v>
+        <v>936.3</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="C26" t="n">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="D26" t="n">
-        <v>929</v>
+        <v>886</v>
       </c>
       <c r="E26" t="n">
-        <v>1014</v>
+        <v>934</v>
       </c>
       <c r="F26" t="n">
-        <v>737</v>
+        <v>813</v>
       </c>
       <c r="G26" t="n">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="H26" t="n">
-        <v>867</v>
+        <v>783</v>
       </c>
       <c r="I26" t="n">
-        <v>843</v>
+        <v>946</v>
       </c>
       <c r="J26" t="n">
-        <v>747</v>
+        <v>732</v>
       </c>
       <c r="K26" t="n">
-        <v>818</v>
+        <v>871</v>
       </c>
       <c r="L26" t="n">
-        <v>841.3</v>
+        <v>842.2</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>996</v>
+        <v>925</v>
       </c>
       <c r="C27" t="n">
-        <v>903</v>
+        <v>1053</v>
       </c>
       <c r="D27" t="n">
-        <v>808</v>
+        <v>931</v>
       </c>
       <c r="E27" t="n">
-        <v>993</v>
+        <v>880</v>
       </c>
       <c r="F27" t="n">
-        <v>1074</v>
+        <v>1045</v>
       </c>
       <c r="G27" t="n">
-        <v>1070</v>
+        <v>883</v>
       </c>
       <c r="H27" t="n">
-        <v>1125</v>
+        <v>970</v>
       </c>
       <c r="I27" t="n">
-        <v>1019</v>
+        <v>888</v>
       </c>
       <c r="J27" t="n">
-        <v>831</v>
+        <v>1067</v>
       </c>
       <c r="K27" t="n">
-        <v>1057</v>
+        <v>1035</v>
       </c>
       <c r="L27" t="n">
-        <v>987.6</v>
+        <v>967.7</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1019</v>
+        <v>954</v>
       </c>
       <c r="C28" t="n">
+        <v>996</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E28" t="n">
+        <v>898</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1064</v>
+      </c>
+      <c r="G28" t="n">
         <v>935</v>
       </c>
-      <c r="D28" t="n">
-        <v>940</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1012</v>
-      </c>
-      <c r="F28" t="n">
-        <v>988</v>
-      </c>
-      <c r="G28" t="n">
-        <v>958</v>
-      </c>
       <c r="H28" t="n">
-        <v>1051</v>
+        <v>1040</v>
       </c>
       <c r="I28" t="n">
-        <v>964</v>
+        <v>992</v>
       </c>
       <c r="J28" t="n">
-        <v>1040</v>
+        <v>1099</v>
       </c>
       <c r="K28" t="n">
-        <v>877</v>
+        <v>1068</v>
       </c>
       <c r="L28" t="n">
-        <v>978.4</v>
+        <v>1008.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>1079</v>
+        <v>1003</v>
       </c>
       <c r="C29" t="n">
-        <v>909</v>
+        <v>878</v>
       </c>
       <c r="D29" t="n">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="E29" t="n">
-        <v>1082</v>
+        <v>976</v>
       </c>
       <c r="F29" t="n">
-        <v>888</v>
+        <v>862</v>
       </c>
       <c r="G29" t="n">
-        <v>1021</v>
+        <v>972</v>
       </c>
       <c r="H29" t="n">
-        <v>858</v>
+        <v>841</v>
       </c>
       <c r="I29" t="n">
-        <v>969</v>
+        <v>1035</v>
       </c>
       <c r="J29" t="n">
-        <v>976</v>
+        <v>943</v>
       </c>
       <c r="K29" t="n">
-        <v>874</v>
+        <v>1016</v>
       </c>
       <c r="L29" t="n">
-        <v>966.2</v>
+        <v>952.9</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1083</v>
+        <v>1051</v>
       </c>
       <c r="C30" t="n">
-        <v>991</v>
+        <v>895</v>
       </c>
       <c r="D30" t="n">
+        <v>981</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1005</v>
+      </c>
+      <c r="F30" t="n">
+        <v>960</v>
+      </c>
+      <c r="G30" t="n">
+        <v>934</v>
+      </c>
+      <c r="H30" t="n">
         <v>993</v>
       </c>
-      <c r="E30" t="n">
-        <v>974</v>
-      </c>
-      <c r="F30" t="n">
-        <v>806</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1037</v>
-      </c>
-      <c r="H30" t="n">
-        <v>919</v>
-      </c>
       <c r="I30" t="n">
-        <v>1171</v>
+        <v>1124</v>
       </c>
       <c r="J30" t="n">
-        <v>971</v>
+        <v>1118</v>
       </c>
       <c r="K30" t="n">
-        <v>915</v>
+        <v>886</v>
       </c>
       <c r="L30" t="n">
-        <v>986</v>
+        <v>994.7</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>907</v>
+        <v>855</v>
       </c>
       <c r="C31" t="n">
-        <v>1053</v>
+        <v>883</v>
       </c>
       <c r="D31" t="n">
-        <v>962</v>
+        <v>916</v>
       </c>
       <c r="E31" t="n">
-        <v>798</v>
+        <v>968</v>
       </c>
       <c r="F31" t="n">
-        <v>891</v>
+        <v>930</v>
       </c>
       <c r="G31" t="n">
-        <v>888</v>
+        <v>964</v>
       </c>
       <c r="H31" t="n">
-        <v>895</v>
+        <v>1018</v>
       </c>
       <c r="I31" t="n">
-        <v>924</v>
+        <v>861</v>
       </c>
       <c r="J31" t="n">
-        <v>816</v>
+        <v>791</v>
       </c>
       <c r="K31" t="n">
-        <v>813</v>
+        <v>935</v>
       </c>
       <c r="L31" t="n">
-        <v>894.7</v>
+        <v>912.1</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>796</v>
+        <v>821</v>
       </c>
       <c r="C32" t="n">
-        <v>1064</v>
+        <v>907</v>
       </c>
       <c r="D32" t="n">
-        <v>922</v>
+        <v>813</v>
       </c>
       <c r="E32" t="n">
-        <v>814</v>
+        <v>785</v>
       </c>
       <c r="F32" t="n">
-        <v>835</v>
+        <v>903</v>
       </c>
       <c r="G32" t="n">
-        <v>811</v>
+        <v>782</v>
       </c>
       <c r="H32" t="n">
-        <v>935</v>
+        <v>944</v>
       </c>
       <c r="I32" t="n">
-        <v>953</v>
+        <v>928</v>
       </c>
       <c r="J32" t="n">
-        <v>935</v>
+        <v>819</v>
       </c>
       <c r="K32" t="n">
-        <v>788</v>
+        <v>806</v>
       </c>
       <c r="L32" t="n">
-        <v>885.3</v>
+        <v>850.8</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>756</v>
+        <v>921</v>
       </c>
       <c r="C33" t="n">
-        <v>802</v>
+        <v>849</v>
       </c>
       <c r="D33" t="n">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="E33" t="n">
-        <v>1029</v>
+        <v>997</v>
       </c>
       <c r="F33" t="n">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="G33" t="n">
-        <v>843</v>
+        <v>960</v>
       </c>
       <c r="H33" t="n">
-        <v>992</v>
+        <v>918</v>
       </c>
       <c r="I33" t="n">
-        <v>785</v>
+        <v>761</v>
       </c>
       <c r="J33" t="n">
-        <v>925</v>
+        <v>1101</v>
       </c>
       <c r="K33" t="n">
-        <v>826</v>
+        <v>791</v>
       </c>
       <c r="L33" t="n">
-        <v>860.2</v>
+        <v>895.8</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="C34" t="n">
-        <v>816</v>
+        <v>894</v>
       </c>
       <c r="D34" t="n">
-        <v>881</v>
+        <v>826</v>
       </c>
       <c r="E34" t="n">
-        <v>854</v>
+        <v>893</v>
       </c>
       <c r="F34" t="n">
-        <v>881</v>
+        <v>956</v>
       </c>
       <c r="G34" t="n">
-        <v>700</v>
+        <v>937</v>
       </c>
       <c r="H34" t="n">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="I34" t="n">
-        <v>830</v>
+        <v>875</v>
       </c>
       <c r="J34" t="n">
-        <v>940</v>
+        <v>974</v>
       </c>
       <c r="K34" t="n">
-        <v>1046</v>
+        <v>829</v>
       </c>
       <c r="L34" t="n">
-        <v>886.6</v>
+        <v>910.8</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>847</v>
+        <v>827</v>
       </c>
       <c r="C35" t="n">
-        <v>974</v>
+        <v>1158</v>
       </c>
       <c r="D35" t="n">
-        <v>760</v>
+        <v>859</v>
       </c>
       <c r="E35" t="n">
-        <v>933</v>
+        <v>845</v>
       </c>
       <c r="F35" t="n">
-        <v>868</v>
+        <v>818</v>
       </c>
       <c r="G35" t="n">
-        <v>729</v>
+        <v>838</v>
       </c>
       <c r="H35" t="n">
-        <v>891</v>
+        <v>857</v>
       </c>
       <c r="I35" t="n">
-        <v>817</v>
+        <v>764</v>
       </c>
       <c r="J35" t="n">
-        <v>789</v>
+        <v>766</v>
       </c>
       <c r="K35" t="n">
-        <v>893</v>
+        <v>872</v>
       </c>
       <c r="L35" t="n">
-        <v>850.1</v>
+        <v>860.4</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>964</v>
+        <v>1131</v>
       </c>
       <c r="C36" t="n">
-        <v>953</v>
+        <v>998</v>
       </c>
       <c r="D36" t="n">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="E36" t="n">
-        <v>889</v>
+        <v>961</v>
       </c>
       <c r="F36" t="n">
-        <v>1037</v>
+        <v>932</v>
       </c>
       <c r="G36" t="n">
-        <v>1214</v>
+        <v>1106</v>
       </c>
       <c r="H36" t="n">
-        <v>1152</v>
+        <v>1049</v>
       </c>
       <c r="I36" t="n">
-        <v>963</v>
+        <v>1062</v>
       </c>
       <c r="J36" t="n">
-        <v>1087</v>
+        <v>1059</v>
       </c>
       <c r="K36" t="n">
-        <v>1156</v>
+        <v>843</v>
       </c>
       <c r="L36" t="n">
-        <v>1038.1</v>
+        <v>1009.6</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>893</v>
+        <v>859</v>
       </c>
       <c r="C37" t="n">
-        <v>877</v>
+        <v>999</v>
       </c>
       <c r="D37" t="n">
-        <v>795</v>
+        <v>850</v>
       </c>
       <c r="E37" t="n">
-        <v>842</v>
+        <v>811</v>
       </c>
       <c r="F37" t="n">
-        <v>797</v>
+        <v>829</v>
       </c>
       <c r="G37" t="n">
-        <v>753</v>
+        <v>898</v>
       </c>
       <c r="H37" t="n">
-        <v>816</v>
+        <v>1016</v>
       </c>
       <c r="I37" t="n">
-        <v>704</v>
+        <v>940</v>
       </c>
       <c r="J37" t="n">
-        <v>904</v>
+        <v>775</v>
       </c>
       <c r="K37" t="n">
-        <v>787</v>
+        <v>898</v>
       </c>
       <c r="L37" t="n">
-        <v>816.8</v>
+        <v>887.5</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>841</v>
+        <v>803</v>
       </c>
       <c r="C38" t="n">
-        <v>935</v>
+        <v>748</v>
       </c>
       <c r="D38" t="n">
-        <v>928</v>
+        <v>852</v>
       </c>
       <c r="E38" t="n">
-        <v>860</v>
+        <v>836</v>
       </c>
       <c r="F38" t="n">
-        <v>804</v>
+        <v>887</v>
       </c>
       <c r="G38" t="n">
-        <v>904</v>
+        <v>929</v>
       </c>
       <c r="H38" t="n">
-        <v>1042</v>
+        <v>842</v>
       </c>
       <c r="I38" t="n">
-        <v>895</v>
+        <v>819</v>
       </c>
       <c r="J38" t="n">
-        <v>793</v>
+        <v>713</v>
       </c>
       <c r="K38" t="n">
-        <v>843</v>
+        <v>901</v>
       </c>
       <c r="L38" t="n">
-        <v>884.5</v>
+        <v>833</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>850</v>
+        <v>805</v>
       </c>
       <c r="C39" t="n">
-        <v>898</v>
+        <v>808</v>
       </c>
       <c r="D39" t="n">
-        <v>700</v>
+        <v>796</v>
       </c>
       <c r="E39" t="n">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="F39" t="n">
-        <v>1068</v>
+        <v>818</v>
       </c>
       <c r="G39" t="n">
-        <v>925</v>
+        <v>755</v>
       </c>
       <c r="H39" t="n">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="I39" t="n">
-        <v>768</v>
+        <v>821</v>
       </c>
       <c r="J39" t="n">
-        <v>699</v>
+        <v>854</v>
       </c>
       <c r="K39" t="n">
-        <v>777</v>
+        <v>822</v>
       </c>
       <c r="L39" t="n">
-        <v>834.1</v>
+        <v>809.3</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1084</v>
+        <v>791</v>
       </c>
       <c r="C40" t="n">
-        <v>799</v>
+        <v>1048</v>
       </c>
       <c r="D40" t="n">
-        <v>810</v>
+        <v>832</v>
       </c>
       <c r="E40" t="n">
-        <v>769</v>
+        <v>846</v>
       </c>
       <c r="F40" t="n">
-        <v>867</v>
+        <v>886</v>
       </c>
       <c r="G40" t="n">
-        <v>1124</v>
+        <v>995</v>
       </c>
       <c r="H40" t="n">
-        <v>829</v>
+        <v>896</v>
       </c>
       <c r="I40" t="n">
-        <v>947</v>
+        <v>835</v>
       </c>
       <c r="J40" t="n">
-        <v>932</v>
+        <v>846</v>
       </c>
       <c r="K40" t="n">
-        <v>1004</v>
+        <v>771</v>
       </c>
       <c r="L40" t="n">
-        <v>916.5</v>
+        <v>874.6</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>1032</v>
+        <v>1018</v>
       </c>
       <c r="C41" t="n">
-        <v>980</v>
+        <v>913</v>
       </c>
       <c r="D41" t="n">
-        <v>946</v>
+        <v>928</v>
       </c>
       <c r="E41" t="n">
-        <v>842</v>
+        <v>930</v>
       </c>
       <c r="F41" t="n">
-        <v>996</v>
+        <v>817</v>
       </c>
       <c r="G41" t="n">
-        <v>802</v>
+        <v>833</v>
       </c>
       <c r="H41" t="n">
-        <v>970</v>
+        <v>1007</v>
       </c>
       <c r="I41" t="n">
-        <v>1029</v>
+        <v>797</v>
       </c>
       <c r="J41" t="n">
-        <v>1117</v>
+        <v>839</v>
       </c>
       <c r="K41" t="n">
-        <v>1069</v>
+        <v>937</v>
       </c>
       <c r="L41" t="n">
-        <v>978.3</v>
+        <v>901.9</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>699</v>
+        <v>955</v>
       </c>
       <c r="C42" t="n">
-        <v>998</v>
+        <v>880</v>
       </c>
       <c r="D42" t="n">
-        <v>898</v>
+        <v>732</v>
       </c>
       <c r="E42" t="n">
-        <v>984</v>
+        <v>933</v>
       </c>
       <c r="F42" t="n">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="G42" t="n">
-        <v>1027</v>
+        <v>1074</v>
       </c>
       <c r="H42" t="n">
-        <v>802</v>
+        <v>812</v>
       </c>
       <c r="I42" t="n">
-        <v>866</v>
+        <v>1012</v>
       </c>
       <c r="J42" t="n">
-        <v>833</v>
+        <v>899</v>
       </c>
       <c r="K42" t="n">
-        <v>923</v>
+        <v>948</v>
       </c>
       <c r="L42" t="n">
-        <v>878.6</v>
+        <v>900.9</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>759</v>
+        <v>942</v>
       </c>
       <c r="C43" t="n">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D43" t="n">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="E43" t="n">
-        <v>871</v>
+        <v>978</v>
       </c>
       <c r="F43" t="n">
-        <v>957</v>
+        <v>974</v>
       </c>
       <c r="G43" t="n">
-        <v>737</v>
+        <v>810</v>
       </c>
       <c r="H43" t="n">
-        <v>748</v>
+        <v>935</v>
       </c>
       <c r="I43" t="n">
-        <v>804</v>
+        <v>761</v>
       </c>
       <c r="J43" t="n">
-        <v>994</v>
+        <v>934</v>
       </c>
       <c r="K43" t="n">
-        <v>861</v>
+        <v>801</v>
       </c>
       <c r="L43" t="n">
-        <v>836.9</v>
+        <v>877.9</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>787</v>
+        <v>990</v>
       </c>
       <c r="C44" t="n">
-        <v>896</v>
+        <v>844</v>
       </c>
       <c r="D44" t="n">
-        <v>826</v>
+        <v>859</v>
       </c>
       <c r="E44" t="n">
-        <v>902</v>
+        <v>828</v>
       </c>
       <c r="F44" t="n">
-        <v>868</v>
+        <v>786</v>
       </c>
       <c r="G44" t="n">
-        <v>1070</v>
+        <v>1036</v>
       </c>
       <c r="H44" t="n">
-        <v>770</v>
+        <v>890</v>
       </c>
       <c r="I44" t="n">
-        <v>820</v>
+        <v>806</v>
       </c>
       <c r="J44" t="n">
-        <v>751</v>
+        <v>946</v>
       </c>
       <c r="K44" t="n">
-        <v>800</v>
+        <v>919</v>
       </c>
       <c r="L44" t="n">
-        <v>849</v>
+        <v>890.4</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>1070</v>
+        <v>983</v>
       </c>
       <c r="C45" t="n">
-        <v>939</v>
+        <v>842</v>
       </c>
       <c r="D45" t="n">
-        <v>929</v>
+        <v>1001</v>
       </c>
       <c r="E45" t="n">
-        <v>853</v>
+        <v>873</v>
       </c>
       <c r="F45" t="n">
-        <v>783</v>
+        <v>893</v>
       </c>
       <c r="G45" t="n">
-        <v>858</v>
+        <v>969</v>
       </c>
       <c r="H45" t="n">
-        <v>969</v>
+        <v>913</v>
       </c>
       <c r="I45" t="n">
-        <v>1089</v>
+        <v>936</v>
       </c>
       <c r="J45" t="n">
-        <v>988</v>
+        <v>802</v>
       </c>
       <c r="K45" t="n">
-        <v>987</v>
+        <v>1111</v>
       </c>
       <c r="L45" t="n">
-        <v>946.5</v>
+        <v>932.3</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>839</v>
+        <v>952</v>
       </c>
       <c r="C46" t="n">
         <v>869</v>
       </c>
       <c r="D46" t="n">
-        <v>975</v>
+        <v>876</v>
       </c>
       <c r="E46" t="n">
-        <v>887</v>
+        <v>939</v>
       </c>
       <c r="F46" t="n">
-        <v>931</v>
+        <v>815</v>
       </c>
       <c r="G46" t="n">
-        <v>815</v>
+        <v>896</v>
       </c>
       <c r="H46" t="n">
-        <v>882</v>
+        <v>803</v>
       </c>
       <c r="I46" t="n">
-        <v>868</v>
+        <v>1054</v>
       </c>
       <c r="J46" t="n">
-        <v>1053</v>
+        <v>850</v>
       </c>
       <c r="K46" t="n">
-        <v>992</v>
+        <v>1006</v>
       </c>
       <c r="L46" t="n">
-        <v>911.1</v>
+        <v>906</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>927</v>
+        <v>972</v>
       </c>
       <c r="C47" t="n">
-        <v>819</v>
+        <v>1122</v>
       </c>
       <c r="D47" t="n">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="E47" t="n">
-        <v>968</v>
+        <v>844</v>
       </c>
       <c r="F47" t="n">
-        <v>927</v>
+        <v>1028</v>
       </c>
       <c r="G47" t="n">
-        <v>999</v>
+        <v>867</v>
       </c>
       <c r="H47" t="n">
-        <v>918</v>
+        <v>814</v>
       </c>
       <c r="I47" t="n">
-        <v>1129</v>
+        <v>1107</v>
       </c>
       <c r="J47" t="n">
-        <v>917</v>
+        <v>1115</v>
       </c>
       <c r="K47" t="n">
-        <v>1115</v>
+        <v>1045</v>
       </c>
       <c r="L47" t="n">
-        <v>976.3</v>
+        <v>995.4</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="C48" t="n">
-        <v>938</v>
+        <v>967</v>
       </c>
       <c r="D48" t="n">
-        <v>898</v>
+        <v>908</v>
       </c>
       <c r="E48" t="n">
-        <v>911</v>
+        <v>1037</v>
       </c>
       <c r="F48" t="n">
-        <v>831</v>
+        <v>959</v>
       </c>
       <c r="G48" t="n">
-        <v>901</v>
+        <v>813</v>
       </c>
       <c r="H48" t="n">
-        <v>847</v>
+        <v>884</v>
       </c>
       <c r="I48" t="n">
-        <v>959</v>
+        <v>867</v>
       </c>
       <c r="J48" t="n">
-        <v>1055</v>
+        <v>980</v>
       </c>
       <c r="K48" t="n">
-        <v>1030</v>
+        <v>888</v>
       </c>
       <c r="L48" t="n">
-        <v>929.1</v>
+        <v>920.8</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>902</v>
+        <v>962</v>
       </c>
       <c r="C49" t="n">
-        <v>978</v>
+        <v>995</v>
       </c>
       <c r="D49" t="n">
-        <v>1005</v>
+        <v>951</v>
       </c>
       <c r="E49" t="n">
-        <v>946</v>
+        <v>1121</v>
       </c>
       <c r="F49" t="n">
-        <v>824</v>
+        <v>787</v>
       </c>
       <c r="G49" t="n">
-        <v>928</v>
+        <v>940</v>
       </c>
       <c r="H49" t="n">
-        <v>1047</v>
+        <v>849</v>
       </c>
       <c r="I49" t="n">
-        <v>915</v>
+        <v>896</v>
       </c>
       <c r="J49" t="n">
-        <v>906</v>
+        <v>985</v>
       </c>
       <c r="K49" t="n">
-        <v>907</v>
+        <v>877</v>
       </c>
       <c r="L49" t="n">
-        <v>935.8</v>
+        <v>936.3</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>967</v>
+        <v>1062</v>
       </c>
       <c r="C50" t="n">
-        <v>973</v>
+        <v>929</v>
       </c>
       <c r="D50" t="n">
-        <v>837</v>
+        <v>874</v>
       </c>
       <c r="E50" t="n">
-        <v>933</v>
+        <v>868</v>
       </c>
       <c r="F50" t="n">
-        <v>858</v>
+        <v>1011</v>
       </c>
       <c r="G50" t="n">
-        <v>971</v>
+        <v>854</v>
       </c>
       <c r="H50" t="n">
-        <v>962</v>
+        <v>864</v>
       </c>
       <c r="I50" t="n">
-        <v>953</v>
+        <v>1017</v>
       </c>
       <c r="J50" t="n">
-        <v>1006</v>
+        <v>959</v>
       </c>
       <c r="K50" t="n">
-        <v>785</v>
+        <v>1002</v>
       </c>
       <c r="L50" t="n">
-        <v>924.5</v>
+        <v>944</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
+        <v>942</v>
+      </c>
+      <c r="C51" t="n">
+        <v>877</v>
+      </c>
+      <c r="D51" t="n">
+        <v>931</v>
+      </c>
+      <c r="E51" t="n">
+        <v>868</v>
+      </c>
+      <c r="F51" t="n">
+        <v>841</v>
+      </c>
+      <c r="G51" t="n">
+        <v>999</v>
+      </c>
+      <c r="H51" t="n">
+        <v>777</v>
+      </c>
+      <c r="I51" t="n">
+        <v>915</v>
+      </c>
+      <c r="J51" t="n">
         <v>889</v>
       </c>
-      <c r="C51" t="n">
-        <v>870</v>
-      </c>
-      <c r="D51" t="n">
-        <v>969</v>
-      </c>
-      <c r="E51" t="n">
-        <v>844</v>
-      </c>
-      <c r="F51" t="n">
-        <v>923</v>
-      </c>
-      <c r="G51" t="n">
-        <v>785</v>
-      </c>
-      <c r="H51" t="n">
-        <v>897</v>
-      </c>
-      <c r="I51" t="n">
-        <v>837</v>
-      </c>
-      <c r="J51" t="n">
-        <v>852</v>
-      </c>
       <c r="K51" t="n">
-        <v>956</v>
+        <v>733</v>
       </c>
       <c r="L51" t="n">
-        <v>882.2</v>
+        <v>877.2</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>915.86</v>
+        <v>921.92</v>
       </c>
       <c r="C52" t="n">
-        <v>919.1799999999999</v>
+        <v>917.58</v>
       </c>
       <c r="D52" t="n">
-        <v>901.26</v>
+        <v>907.88</v>
       </c>
       <c r="E52" t="n">
-        <v>910.12</v>
+        <v>910.88</v>
       </c>
       <c r="F52" t="n">
-        <v>905.8</v>
+        <v>885.98</v>
       </c>
       <c r="G52" t="n">
-        <v>908.5</v>
+        <v>926.52</v>
       </c>
       <c r="H52" t="n">
-        <v>930.24</v>
+        <v>895.48</v>
       </c>
       <c r="I52" t="n">
-        <v>915.08</v>
+        <v>917.88</v>
       </c>
       <c r="J52" t="n">
-        <v>904.2</v>
+        <v>930.4400000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>936.16</v>
+        <v>923.24</v>
       </c>
       <c r="L52" t="n">
-        <v>914.64</v>
+        <v>913.78</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>8.238557100296021</v>
+        <v>8.606063365936279</v>
       </c>
       <c r="C2" t="n">
-        <v>9.037511110305786</v>
+        <v>7.567226409912109</v>
       </c>
       <c r="D2" t="n">
-        <v>8.064501523971558</v>
+        <v>7.198681354522705</v>
       </c>
       <c r="E2" t="n">
-        <v>6.948402881622314</v>
+        <v>10.59502267837524</v>
       </c>
       <c r="F2" t="n">
-        <v>7.714451789855957</v>
+        <v>7.0729660987854</v>
       </c>
       <c r="G2" t="n">
-        <v>7.153435468673706</v>
+        <v>8.259440422058105</v>
       </c>
       <c r="H2" t="n">
-        <v>8.349766731262207</v>
+        <v>7.743764638900757</v>
       </c>
       <c r="I2" t="n">
-        <v>7.383294343948364</v>
+        <v>8.464952230453491</v>
       </c>
       <c r="J2" t="n">
-        <v>7.060127019882202</v>
+        <v>7.079940319061279</v>
       </c>
       <c r="K2" t="n">
-        <v>7.464569568634033</v>
+        <v>8.658454418182373</v>
       </c>
       <c r="L2" t="n">
-        <v>7.741461753845215</v>
+        <v>8.124651193618774</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>8.276970863342285</v>
+        <v>9.270353078842163</v>
       </c>
       <c r="C3" t="n">
-        <v>6.84716272354126</v>
+        <v>8.444973707199097</v>
       </c>
       <c r="D3" t="n">
-        <v>6.801328182220459</v>
+        <v>7.151280164718628</v>
       </c>
       <c r="E3" t="n">
-        <v>6.862350702285767</v>
+        <v>8.097858190536499</v>
       </c>
       <c r="F3" t="n">
-        <v>6.407681226730347</v>
+        <v>8.243004322052002</v>
       </c>
       <c r="G3" t="n">
-        <v>7.696413993835449</v>
+        <v>7.713843822479248</v>
       </c>
       <c r="H3" t="n">
-        <v>8.197152853012085</v>
+        <v>9.447909116744995</v>
       </c>
       <c r="I3" t="n">
-        <v>8.398591279983521</v>
+        <v>7.815078020095825</v>
       </c>
       <c r="J3" t="n">
-        <v>6.539839267730713</v>
+        <v>8.204097747802734</v>
       </c>
       <c r="K3" t="n">
-        <v>8.17715859413147</v>
+        <v>9.261407375335693</v>
       </c>
       <c r="L3" t="n">
-        <v>7.420464968681335</v>
+        <v>8.364980554580688</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>8.294372081756592</v>
+        <v>7.486928224563599</v>
       </c>
       <c r="C4" t="n">
-        <v>8.253967046737671</v>
+        <v>7.364234924316406</v>
       </c>
       <c r="D4" t="n">
-        <v>6.439578533172607</v>
+        <v>8.799563884735107</v>
       </c>
       <c r="E4" t="n">
-        <v>7.339303016662598</v>
+        <v>6.73832368850708</v>
       </c>
       <c r="F4" t="n">
-        <v>7.108900308609009</v>
+        <v>6.691442966461182</v>
       </c>
       <c r="G4" t="n">
-        <v>6.467038154602051</v>
+        <v>9.291359901428223</v>
       </c>
       <c r="H4" t="n">
-        <v>5.971821784973145</v>
+        <v>7.286925077438354</v>
       </c>
       <c r="I4" t="n">
-        <v>6.606644868850708</v>
+        <v>6.371761560440063</v>
       </c>
       <c r="J4" t="n">
-        <v>6.087080717086792</v>
+        <v>6.811636924743652</v>
       </c>
       <c r="K4" t="n">
-        <v>7.427110910415649</v>
+        <v>8.407049655914307</v>
       </c>
       <c r="L4" t="n">
-        <v>6.999581742286682</v>
+        <v>7.524922680854798</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>7.914346218109131</v>
+        <v>7.386178255081177</v>
       </c>
       <c r="C5" t="n">
-        <v>5.794299125671387</v>
+        <v>6.865474939346313</v>
       </c>
       <c r="D5" t="n">
-        <v>8.278387069702148</v>
+        <v>6.409670829772949</v>
       </c>
       <c r="E5" t="n">
-        <v>5.851071834564209</v>
+        <v>6.00070333480835</v>
       </c>
       <c r="F5" t="n">
-        <v>6.608175992965698</v>
+        <v>6.409675121307373</v>
       </c>
       <c r="G5" t="n">
-        <v>7.605617761611938</v>
+        <v>7.380677700042725</v>
       </c>
       <c r="H5" t="n">
-        <v>6.825607776641846</v>
+        <v>6.270539999008179</v>
       </c>
       <c r="I5" t="n">
-        <v>6.763134717941284</v>
+        <v>6.909908533096313</v>
       </c>
       <c r="J5" t="n">
-        <v>5.403930425643921</v>
+        <v>8.167711973190308</v>
       </c>
       <c r="K5" t="n">
-        <v>5.545566558837891</v>
+        <v>8.728817701339722</v>
       </c>
       <c r="L5" t="n">
-        <v>6.659013748168945</v>
+        <v>7.052935838699341</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>5.508169889450073</v>
+        <v>6.092460632324219</v>
       </c>
       <c r="C6" t="n">
-        <v>5.576995611190796</v>
+        <v>6.073053359985352</v>
       </c>
       <c r="D6" t="n">
-        <v>5.745059013366699</v>
+        <v>5.619692325592041</v>
       </c>
       <c r="E6" t="n">
-        <v>5.180015325546265</v>
+        <v>6.251049280166626</v>
       </c>
       <c r="F6" t="n">
-        <v>5.764991283416748</v>
+        <v>6.071015357971191</v>
       </c>
       <c r="G6" t="n">
-        <v>5.189510345458984</v>
+        <v>6.602179527282715</v>
       </c>
       <c r="H6" t="n">
-        <v>5.57999849319458</v>
+        <v>6.010703563690186</v>
       </c>
       <c r="I6" t="n">
-        <v>5.56354022026062</v>
+        <v>6.50193190574646</v>
       </c>
       <c r="J6" t="n">
-        <v>5.75653338432312</v>
+        <v>7.578204393386841</v>
       </c>
       <c r="K6" t="n">
-        <v>5.713649034500122</v>
+        <v>5.815853357315063</v>
       </c>
       <c r="L6" t="n">
-        <v>5.557846260070801</v>
+        <v>6.261614370346069</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>7.622230291366577</v>
+        <v>7.800881624221802</v>
       </c>
       <c r="C7" t="n">
-        <v>7.918914556503296</v>
+        <v>7.51535701751709</v>
       </c>
       <c r="D7" t="n">
-        <v>6.713050127029419</v>
+        <v>7.23509955406189</v>
       </c>
       <c r="E7" t="n">
-        <v>10.68225812911987</v>
+        <v>7.684427738189697</v>
       </c>
       <c r="F7" t="n">
-        <v>7.752408742904663</v>
+        <v>10.15512180328369</v>
       </c>
       <c r="G7" t="n">
-        <v>7.97566556930542</v>
+        <v>9.83892297744751</v>
       </c>
       <c r="H7" t="n">
-        <v>8.781119585037231</v>
+        <v>7.257487058639526</v>
       </c>
       <c r="I7" t="n">
-        <v>7.569720029830933</v>
+        <v>8.259462118148804</v>
       </c>
       <c r="J7" t="n">
-        <v>8.406566381454468</v>
+        <v>6.971742391586304</v>
       </c>
       <c r="K7" t="n">
-        <v>8.150758266448975</v>
+        <v>7.756294965744019</v>
       </c>
       <c r="L7" t="n">
-        <v>8.157269167900086</v>
+        <v>8.047479724884033</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>8.155262231826782</v>
+        <v>9.378601551055908</v>
       </c>
       <c r="C8" t="n">
-        <v>7.145302534103394</v>
+        <v>7.350281000137329</v>
       </c>
       <c r="D8" t="n">
-        <v>8.814535140991211</v>
+        <v>6.988219738006592</v>
       </c>
       <c r="E8" t="n">
-        <v>7.248553037643433</v>
+        <v>7.563208103179932</v>
       </c>
       <c r="F8" t="n">
-        <v>10.08477997779846</v>
+        <v>8.025576591491699</v>
       </c>
       <c r="G8" t="n">
-        <v>6.842568874359131</v>
+        <v>7.636544227600098</v>
       </c>
       <c r="H8" t="n">
-        <v>9.968104124069214</v>
+        <v>9.295857906341553</v>
       </c>
       <c r="I8" t="n">
-        <v>9.550370693206787</v>
+        <v>11.17511105537415</v>
       </c>
       <c r="J8" t="n">
-        <v>6.235779523849487</v>
+        <v>9.807045698165894</v>
       </c>
       <c r="K8" t="n">
-        <v>6.81327748298645</v>
+        <v>10.80953526496887</v>
       </c>
       <c r="L8" t="n">
-        <v>8.085853362083435</v>
+        <v>8.802998113632203</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>6.726992130279541</v>
+        <v>9.368922710418701</v>
       </c>
       <c r="C9" t="n">
-        <v>8.516386270523071</v>
+        <v>9.317763805389404</v>
       </c>
       <c r="D9" t="n">
-        <v>7.081578016281128</v>
+        <v>7.382189512252808</v>
       </c>
       <c r="E9" t="n">
-        <v>8.388170719146729</v>
+        <v>8.091439247131348</v>
       </c>
       <c r="F9" t="n">
-        <v>6.528519868850708</v>
+        <v>9.915205717086792</v>
       </c>
       <c r="G9" t="n">
-        <v>6.964891195297241</v>
+        <v>7.305877208709717</v>
       </c>
       <c r="H9" t="n">
-        <v>6.394856691360474</v>
+        <v>7.514364242553711</v>
       </c>
       <c r="I9" t="n">
-        <v>6.836700201034546</v>
+        <v>7.618582248687744</v>
       </c>
       <c r="J9" t="n">
-        <v>6.418300867080688</v>
+        <v>7.290920257568359</v>
       </c>
       <c r="K9" t="n">
-        <v>9.029587507247925</v>
+        <v>9.499273061752319</v>
       </c>
       <c r="L9" t="n">
-        <v>7.288598346710205</v>
+        <v>8.330453801155091</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>6.327066421508789</v>
+        <v>8.885339260101318</v>
       </c>
       <c r="C10" t="n">
-        <v>7.028706550598145</v>
+        <v>7.494885444641113</v>
       </c>
       <c r="D10" t="n">
-        <v>7.808673620223999</v>
+        <v>6.395689964294434</v>
       </c>
       <c r="E10" t="n">
-        <v>7.495027303695679</v>
+        <v>6.361920356750488</v>
       </c>
       <c r="F10" t="n">
-        <v>8.962191820144653</v>
+        <v>6.446563720703125</v>
       </c>
       <c r="G10" t="n">
-        <v>8.839989900588989</v>
+        <v>7.729780912399292</v>
       </c>
       <c r="H10" t="n">
-        <v>8.173724412918091</v>
+        <v>8.404579639434814</v>
       </c>
       <c r="I10" t="n">
-        <v>6.178430318832397</v>
+        <v>6.92688250541687</v>
       </c>
       <c r="J10" t="n">
-        <v>7.282570362091064</v>
+        <v>6.616128921508789</v>
       </c>
       <c r="K10" t="n">
-        <v>9.884763479232788</v>
+        <v>8.404605388641357</v>
       </c>
       <c r="L10" t="n">
-        <v>7.798114418983459</v>
+        <v>7.366637611389161</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>7.33041787147522</v>
+        <v>8.626023054122925</v>
       </c>
       <c r="C11" t="n">
-        <v>6.555941581726074</v>
+        <v>8.886842489242554</v>
       </c>
       <c r="D11" t="n">
-        <v>5.910141706466675</v>
+        <v>8.94570517539978</v>
       </c>
       <c r="E11" t="n">
-        <v>7.211755037307739</v>
+        <v>10.18103075027466</v>
       </c>
       <c r="F11" t="n">
-        <v>6.784351110458374</v>
+        <v>7.68540358543396</v>
       </c>
       <c r="G11" t="n">
-        <v>6.567956686019897</v>
+        <v>10.0164783000946</v>
       </c>
       <c r="H11" t="n">
-        <v>9.235628843307495</v>
+        <v>7.042032718658447</v>
       </c>
       <c r="I11" t="n">
-        <v>6.660678148269653</v>
+        <v>8.148255109786987</v>
       </c>
       <c r="J11" t="n">
-        <v>6.552948236465454</v>
+        <v>7.735813140869141</v>
       </c>
       <c r="K11" t="n">
-        <v>6.160479307174683</v>
+        <v>8.420532941818237</v>
       </c>
       <c r="L11" t="n">
-        <v>6.897029852867126</v>
+        <v>8.568811726570129</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>7.148405313491821</v>
+        <v>9.441337823867798</v>
       </c>
       <c r="C12" t="n">
-        <v>9.887315988540649</v>
+        <v>9.440926313400269</v>
       </c>
       <c r="D12" t="n">
-        <v>6.68511700630188</v>
+        <v>8.763367414474487</v>
       </c>
       <c r="E12" t="n">
-        <v>6.908557891845703</v>
+        <v>10.61692214012146</v>
       </c>
       <c r="F12" t="n">
-        <v>9.340189456939697</v>
+        <v>7.795142412185669</v>
       </c>
       <c r="G12" t="n">
-        <v>9.88677453994751</v>
+        <v>7.66546106338501</v>
       </c>
       <c r="H12" t="n">
-        <v>8.147295951843262</v>
+        <v>7.395145177841187</v>
       </c>
       <c r="I12" t="n">
-        <v>11.18544173240662</v>
+        <v>11.31662249565125</v>
       </c>
       <c r="J12" t="n">
-        <v>8.058548927307129</v>
+        <v>11.04782104492188</v>
       </c>
       <c r="K12" t="n">
-        <v>10.29873299598694</v>
+        <v>9.557163000106812</v>
       </c>
       <c r="L12" t="n">
-        <v>8.754637980461121</v>
+        <v>9.303990888595582</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>7.233194351196289</v>
+        <v>7.366711378097534</v>
       </c>
       <c r="C13" t="n">
-        <v>6.833237886428833</v>
+        <v>6.662549018859863</v>
       </c>
       <c r="D13" t="n">
-        <v>7.588249683380127</v>
+        <v>8.609554767608643</v>
       </c>
       <c r="E13" t="n">
-        <v>8.294952392578125</v>
+        <v>7.822041273117065</v>
       </c>
       <c r="F13" t="n">
-        <v>6.64669132232666</v>
+        <v>6.888410329818726</v>
       </c>
       <c r="G13" t="n">
-        <v>5.54410719871521</v>
+        <v>6.709397792816162</v>
       </c>
       <c r="H13" t="n">
-        <v>7.96926736831665</v>
+        <v>7.039042472839355</v>
       </c>
       <c r="I13" t="n">
-        <v>5.982036590576172</v>
+        <v>6.35480260848999</v>
       </c>
       <c r="J13" t="n">
-        <v>6.949343681335449</v>
+        <v>9.228491306304932</v>
       </c>
       <c r="K13" t="n">
-        <v>5.833154201507568</v>
+        <v>6.477996110916138</v>
       </c>
       <c r="L13" t="n">
-        <v>6.887423467636109</v>
+        <v>7.31589970588684</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>8.354198217391968</v>
+        <v>7.607675552368164</v>
       </c>
       <c r="C14" t="n">
-        <v>6.676512241363525</v>
+        <v>8.282422780990601</v>
       </c>
       <c r="D14" t="n">
-        <v>7.045028448104858</v>
+        <v>7.458472728729248</v>
       </c>
       <c r="E14" t="n">
-        <v>7.151796102523804</v>
+        <v>8.640978336334229</v>
       </c>
       <c r="F14" t="n">
-        <v>9.278353452682495</v>
+        <v>7.075980186462402</v>
       </c>
       <c r="G14" t="n">
-        <v>8.743237733840942</v>
+        <v>9.562516212463379</v>
       </c>
       <c r="H14" t="n">
-        <v>7.325866460800171</v>
+        <v>7.921864748001099</v>
       </c>
       <c r="I14" t="n">
-        <v>6.653594017028809</v>
+        <v>8.572187662124634</v>
       </c>
       <c r="J14" t="n">
-        <v>7.337774753570557</v>
+        <v>10.94949293136597</v>
       </c>
       <c r="K14" t="n">
-        <v>6.553783893585205</v>
+        <v>8.416108131408691</v>
       </c>
       <c r="L14" t="n">
-        <v>7.512014532089234</v>
+        <v>8.448769927024841</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>7.474947214126587</v>
+        <v>7.205235242843628</v>
       </c>
       <c r="C15" t="n">
-        <v>9.208198308944702</v>
+        <v>7.530892848968506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.633731126785278</v>
+        <v>10.59242916107178</v>
       </c>
       <c r="E15" t="n">
-        <v>7.509956121444702</v>
+        <v>7.465564727783203</v>
       </c>
       <c r="F15" t="n">
-        <v>7.97327709197998</v>
+        <v>7.925891637802124</v>
       </c>
       <c r="G15" t="n">
-        <v>6.626754760742188</v>
+        <v>7.783711671829224</v>
       </c>
       <c r="H15" t="n">
-        <v>7.430663824081421</v>
+        <v>7.232158422470093</v>
       </c>
       <c r="I15" t="n">
-        <v>7.20527982711792</v>
+        <v>9.808455228805542</v>
       </c>
       <c r="J15" t="n">
-        <v>6.585441589355469</v>
+        <v>6.539496183395386</v>
       </c>
       <c r="K15" t="n">
-        <v>6.766418218612671</v>
+        <v>7.241155862808228</v>
       </c>
       <c r="L15" t="n">
-        <v>7.341466808319092</v>
+        <v>7.932499098777771</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>7.512963533401489</v>
+        <v>7.981731414794922</v>
       </c>
       <c r="C16" t="n">
-        <v>6.580878973007202</v>
+        <v>7.023714542388916</v>
       </c>
       <c r="D16" t="n">
-        <v>7.795202732086182</v>
+        <v>8.180716991424561</v>
       </c>
       <c r="E16" t="n">
-        <v>6.42826247215271</v>
+        <v>6.942412614822388</v>
       </c>
       <c r="F16" t="n">
-        <v>7.604211807250977</v>
+        <v>8.068488836288452</v>
       </c>
       <c r="G16" t="n">
-        <v>6.544969320297241</v>
+        <v>7.07759690284729</v>
       </c>
       <c r="H16" t="n">
-        <v>6.086191415786743</v>
+        <v>7.804683923721313</v>
       </c>
       <c r="I16" t="n">
-        <v>7.314473867416382</v>
+        <v>8.708832740783691</v>
       </c>
       <c r="J16" t="n">
-        <v>7.06511926651001</v>
+        <v>7.15145206451416</v>
       </c>
       <c r="K16" t="n">
-        <v>8.610625982284546</v>
+        <v>7.416716575622559</v>
       </c>
       <c r="L16" t="n">
-        <v>7.154289937019348</v>
+        <v>7.635634660720825</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>7.028715133666992</v>
+        <v>7.817681074142456</v>
       </c>
       <c r="C17" t="n">
-        <v>6.854257106781006</v>
+        <v>8.528289318084717</v>
       </c>
       <c r="D17" t="n">
-        <v>6.569962024688721</v>
+        <v>9.153677701950073</v>
       </c>
       <c r="E17" t="n">
-        <v>8.810065031051636</v>
+        <v>10.33164811134338</v>
       </c>
       <c r="F17" t="n">
-        <v>6.889585256576538</v>
+        <v>8.099440097808838</v>
       </c>
       <c r="G17" t="n">
-        <v>7.741372346878052</v>
+        <v>8.046056270599365</v>
       </c>
       <c r="H17" t="n">
-        <v>6.838805675506592</v>
+        <v>7.20125150680542</v>
       </c>
       <c r="I17" t="n">
-        <v>9.227466821670532</v>
+        <v>7.878032684326172</v>
       </c>
       <c r="J17" t="n">
-        <v>6.55579400062561</v>
+        <v>7.103014230728149</v>
       </c>
       <c r="K17" t="n">
-        <v>7.426607370376587</v>
+        <v>7.26406455039978</v>
       </c>
       <c r="L17" t="n">
-        <v>7.394263076782226</v>
+        <v>8.142315554618836</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>7.200121879577637</v>
+        <v>10.10719060897827</v>
       </c>
       <c r="C18" t="n">
-        <v>7.198670864105225</v>
+        <v>7.643081665039062</v>
       </c>
       <c r="D18" t="n">
-        <v>6.99319863319397</v>
+        <v>7.818143606185913</v>
       </c>
       <c r="E18" t="n">
-        <v>8.195134162902832</v>
+        <v>6.845190286636353</v>
       </c>
       <c r="F18" t="n">
-        <v>9.696374654769897</v>
+        <v>6.873099088668823</v>
       </c>
       <c r="G18" t="n">
-        <v>8.08391547203064</v>
+        <v>8.041295528411865</v>
       </c>
       <c r="H18" t="n">
-        <v>7.132317066192627</v>
+        <v>6.995682239532471</v>
       </c>
       <c r="I18" t="n">
-        <v>6.334419727325439</v>
+        <v>8.024513244628906</v>
       </c>
       <c r="J18" t="n">
-        <v>7.554747819900513</v>
+        <v>7.114377737045288</v>
       </c>
       <c r="K18" t="n">
-        <v>6.916885137557983</v>
+        <v>8.545243263244629</v>
       </c>
       <c r="L18" t="n">
-        <v>7.530578541755676</v>
+        <v>7.800781726837158</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>6.556820154190063</v>
+        <v>6.573733806610107</v>
       </c>
       <c r="C19" t="n">
-        <v>7.154750108718872</v>
+        <v>7.09044075012207</v>
       </c>
       <c r="D19" t="n">
-        <v>6.232146263122559</v>
+        <v>6.444560766220093</v>
       </c>
       <c r="E19" t="n">
-        <v>5.941345453262329</v>
+        <v>6.526393413543701</v>
       </c>
       <c r="F19" t="n">
-        <v>7.175756692886353</v>
+        <v>6.627097129821777</v>
       </c>
       <c r="G19" t="n">
-        <v>7.15325140953064</v>
+        <v>7.775647640228271</v>
       </c>
       <c r="H19" t="n">
-        <v>7.005394697189331</v>
+        <v>8.029544115066528</v>
       </c>
       <c r="I19" t="n">
-        <v>7.852564573287964</v>
+        <v>7.794105052947998</v>
       </c>
       <c r="J19" t="n">
-        <v>5.872219562530518</v>
+        <v>7.076483964920044</v>
       </c>
       <c r="K19" t="n">
-        <v>6.183909177780151</v>
+        <v>7.870925903320312</v>
       </c>
       <c r="L19" t="n">
-        <v>6.712815809249878</v>
+        <v>7.180893254280091</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>6.649685382843018</v>
+        <v>7.157271385192871</v>
       </c>
       <c r="C20" t="n">
-        <v>6.860666990280151</v>
+        <v>7.444030046463013</v>
       </c>
       <c r="D20" t="n">
-        <v>8.582224607467651</v>
+        <v>6.590211868286133</v>
       </c>
       <c r="E20" t="n">
-        <v>7.699544429779053</v>
+        <v>7.114360570907593</v>
       </c>
       <c r="F20" t="n">
-        <v>6.641726016998291</v>
+        <v>7.700868606567383</v>
       </c>
       <c r="G20" t="n">
-        <v>8.934249401092529</v>
+        <v>7.330824851989746</v>
       </c>
       <c r="H20" t="n">
-        <v>8.732779979705811</v>
+        <v>10.02843141555786</v>
       </c>
       <c r="I20" t="n">
-        <v>6.763392210006714</v>
+        <v>10.30248641967773</v>
       </c>
       <c r="J20" t="n">
-        <v>6.969916343688965</v>
+        <v>9.481330394744873</v>
       </c>
       <c r="K20" t="n">
-        <v>9.059436082839966</v>
+        <v>7.344976663589478</v>
       </c>
       <c r="L20" t="n">
-        <v>7.689362144470214</v>
+        <v>8.049479222297668</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>6.563920974731445</v>
+        <v>6.874083280563354</v>
       </c>
       <c r="C21" t="n">
-        <v>7.105500221252441</v>
+        <v>8.40775990486145</v>
       </c>
       <c r="D21" t="n">
-        <v>7.060148000717163</v>
+        <v>8.357180833816528</v>
       </c>
       <c r="E21" t="n">
-        <v>6.6921067237854</v>
+        <v>7.883721351623535</v>
       </c>
       <c r="F21" t="n">
-        <v>7.875507593154907</v>
+        <v>7.328423738479614</v>
       </c>
       <c r="G21" t="n">
-        <v>6.439935684204102</v>
+        <v>10.25421094894409</v>
       </c>
       <c r="H21" t="n">
-        <v>8.017154216766357</v>
+        <v>9.153376579284668</v>
       </c>
       <c r="I21" t="n">
-        <v>7.715428352355957</v>
+        <v>9.370123624801636</v>
       </c>
       <c r="J21" t="n">
-        <v>8.474439144134521</v>
+        <v>7.153372764587402</v>
       </c>
       <c r="K21" t="n">
-        <v>8.069007396697998</v>
+        <v>10.35552406311035</v>
       </c>
       <c r="L21" t="n">
-        <v>7.401314830780029</v>
+        <v>8.513777709007263</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>6.500468254089355</v>
+        <v>7.435153245925903</v>
       </c>
       <c r="C22" t="n">
-        <v>7.265979051589966</v>
+        <v>6.306581258773804</v>
       </c>
       <c r="D22" t="n">
-        <v>6.164795875549316</v>
+        <v>9.158170938491821</v>
       </c>
       <c r="E22" t="n">
-        <v>5.944862127304077</v>
+        <v>8.124167203903198</v>
       </c>
       <c r="F22" t="n">
-        <v>5.63364839553833</v>
+        <v>6.438606262207031</v>
       </c>
       <c r="G22" t="n">
-        <v>5.619721174240112</v>
+        <v>7.212628126144409</v>
       </c>
       <c r="H22" t="n">
-        <v>7.054025650024414</v>
+        <v>6.87997031211853</v>
       </c>
       <c r="I22" t="n">
-        <v>5.702986240386963</v>
+        <v>7.92731499671936</v>
       </c>
       <c r="J22" t="n">
-        <v>5.498512029647827</v>
+        <v>6.867460966110229</v>
       </c>
       <c r="K22" t="n">
-        <v>6.673517465591431</v>
+        <v>6.891937494277954</v>
       </c>
       <c r="L22" t="n">
-        <v>6.205851626396179</v>
+        <v>7.324199080467224</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>7.803127527236938</v>
+        <v>9.472376585006714</v>
       </c>
       <c r="C23" t="n">
-        <v>8.305348873138428</v>
+        <v>8.875405788421631</v>
       </c>
       <c r="D23" t="n">
-        <v>8.425539255142212</v>
+        <v>7.860447406768799</v>
       </c>
       <c r="E23" t="n">
-        <v>8.060451745986938</v>
+        <v>9.075851678848267</v>
       </c>
       <c r="F23" t="n">
-        <v>7.119376420974731</v>
+        <v>9.406010389328003</v>
       </c>
       <c r="G23" t="n">
-        <v>8.443501472473145</v>
+        <v>10.25933814048767</v>
       </c>
       <c r="H23" t="n">
-        <v>8.061959266662598</v>
+        <v>7.47492790222168</v>
       </c>
       <c r="I23" t="n">
-        <v>8.763179063796997</v>
+        <v>8.811513662338257</v>
       </c>
       <c r="J23" t="n">
-        <v>7.777168273925781</v>
+        <v>9.178655624389648</v>
       </c>
       <c r="K23" t="n">
-        <v>8.631058931350708</v>
+        <v>9.364639282226562</v>
       </c>
       <c r="L23" t="n">
-        <v>8.139071083068847</v>
+        <v>8.977916646003724</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>7.456007719039917</v>
+        <v>11.26978421211243</v>
       </c>
       <c r="C24" t="n">
-        <v>8.330803155899048</v>
+        <v>11.38448238372803</v>
       </c>
       <c r="D24" t="n">
-        <v>7.339794397354126</v>
+        <v>11.45231699943542</v>
       </c>
       <c r="E24" t="n">
-        <v>9.739702224731445</v>
+        <v>10.72317099571228</v>
       </c>
       <c r="F24" t="n">
-        <v>8.102914810180664</v>
+        <v>10.87227272987366</v>
       </c>
       <c r="G24" t="n">
-        <v>8.625021696090698</v>
+        <v>10.47605895996094</v>
       </c>
       <c r="H24" t="n">
-        <v>9.580065488815308</v>
+        <v>10.23834133148193</v>
       </c>
       <c r="I24" t="n">
-        <v>9.523223638534546</v>
+        <v>7.433645963668823</v>
       </c>
       <c r="J24" t="n">
-        <v>10.38652849197388</v>
+        <v>10.06582474708557</v>
       </c>
       <c r="K24" t="n">
-        <v>9.133214235305786</v>
+        <v>8.746298789978027</v>
       </c>
       <c r="L24" t="n">
-        <v>8.821727585792541</v>
+        <v>10.26621971130371</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>6.423650979995728</v>
+        <v>6.786431550979614</v>
       </c>
       <c r="C25" t="n">
-        <v>6.916890621185303</v>
+        <v>10.37602496147156</v>
       </c>
       <c r="D25" t="n">
-        <v>6.296467065811157</v>
+        <v>7.483456373214722</v>
       </c>
       <c r="E25" t="n">
-        <v>7.114376544952393</v>
+        <v>6.7787184715271</v>
       </c>
       <c r="F25" t="n">
-        <v>6.78870964050293</v>
+        <v>7.419080972671509</v>
       </c>
       <c r="G25" t="n">
-        <v>5.99871301651001</v>
+        <v>6.962795495986938</v>
       </c>
       <c r="H25" t="n">
-        <v>6.210170984268188</v>
+        <v>8.127844572067261</v>
       </c>
       <c r="I25" t="n">
-        <v>8.564677715301514</v>
+        <v>6.919889211654663</v>
       </c>
       <c r="J25" t="n">
-        <v>9.027973651885986</v>
+        <v>9.196581125259399</v>
       </c>
       <c r="K25" t="n">
-        <v>9.075402975082397</v>
+        <v>7.442050933837891</v>
       </c>
       <c r="L25" t="n">
-        <v>7.24170331954956</v>
+        <v>7.749287366867065</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>6.136847496032715</v>
+        <v>6.80318546295166</v>
       </c>
       <c r="C26" t="n">
-        <v>6.425624370574951</v>
+        <v>6.784725666046143</v>
       </c>
       <c r="D26" t="n">
-        <v>8.371688365936279</v>
+        <v>9.337703227996826</v>
       </c>
       <c r="E26" t="n">
-        <v>7.48989462852478</v>
+        <v>8.865885257720947</v>
       </c>
       <c r="F26" t="n">
-        <v>6.128393888473511</v>
+        <v>6.770246028900146</v>
       </c>
       <c r="G26" t="n">
-        <v>7.180325031280518</v>
+        <v>6.789695024490356</v>
       </c>
       <c r="H26" t="n">
-        <v>6.041628122329712</v>
+        <v>6.946789979934692</v>
       </c>
       <c r="I26" t="n">
-        <v>6.213183641433716</v>
+        <v>9.368130445480347</v>
       </c>
       <c r="J26" t="n">
-        <v>6.555345058441162</v>
+        <v>6.808651924133301</v>
       </c>
       <c r="K26" t="n">
-        <v>6.281976461410522</v>
+        <v>7.278509378433228</v>
       </c>
       <c r="L26" t="n">
-        <v>6.682490706443787</v>
+        <v>7.575352239608764</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>8.641950368881226</v>
+        <v>7.442035436630249</v>
       </c>
       <c r="C27" t="n">
-        <v>6.357815980911255</v>
+        <v>11.15105032920837</v>
       </c>
       <c r="D27" t="n">
-        <v>6.465529680252075</v>
+        <v>9.209758758544922</v>
       </c>
       <c r="E27" t="n">
-        <v>9.729694843292236</v>
+        <v>7.423734188079834</v>
       </c>
       <c r="F27" t="n">
-        <v>8.885866165161133</v>
+        <v>10.32662582397461</v>
       </c>
       <c r="G27" t="n">
-        <v>10.14363694190979</v>
+        <v>7.236199855804443</v>
       </c>
       <c r="H27" t="n">
-        <v>9.067551851272583</v>
+        <v>7.517928123474121</v>
       </c>
       <c r="I27" t="n">
-        <v>7.840601921081543</v>
+        <v>7.517958164215088</v>
       </c>
       <c r="J27" t="n">
-        <v>6.543495178222656</v>
+        <v>9.983025074005127</v>
       </c>
       <c r="K27" t="n">
-        <v>9.124756097793579</v>
+        <v>11.08768796920776</v>
       </c>
       <c r="L27" t="n">
-        <v>8.280089902877808</v>
+        <v>8.889600372314453</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>8.225623369216919</v>
+        <v>9.813469409942627</v>
       </c>
       <c r="C28" t="n">
-        <v>6.679512739181519</v>
+        <v>9.054143190383911</v>
       </c>
       <c r="D28" t="n">
-        <v>8.695363998413086</v>
+        <v>8.078924179077148</v>
       </c>
       <c r="E28" t="n">
-        <v>9.194589853286743</v>
+        <v>7.310857057571411</v>
       </c>
       <c r="F28" t="n">
-        <v>9.125220537185669</v>
+        <v>11.07280158996582</v>
       </c>
       <c r="G28" t="n">
-        <v>7.204135894775391</v>
+        <v>8.741912603378296</v>
       </c>
       <c r="H28" t="n">
-        <v>7.37324333190918</v>
+        <v>10.29020261764526</v>
       </c>
       <c r="I28" t="n">
-        <v>8.601087331771851</v>
+        <v>8.870843172073364</v>
       </c>
       <c r="J28" t="n">
-        <v>8.372134923934937</v>
+        <v>9.794528484344482</v>
       </c>
       <c r="K28" t="n">
-        <v>6.837567567825317</v>
+        <v>9.822970390319824</v>
       </c>
       <c r="L28" t="n">
-        <v>8.030847954750062</v>
+        <v>9.285065269470214</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>7.93626856803894</v>
+        <v>9.6623694896698</v>
       </c>
       <c r="C29" t="n">
-        <v>8.390631914138794</v>
+        <v>8.784590721130371</v>
       </c>
       <c r="D29" t="n">
-        <v>7.967221021652222</v>
+        <v>10.87730360031128</v>
       </c>
       <c r="E29" t="n">
-        <v>10.19103264808655</v>
+        <v>10.00048828125</v>
       </c>
       <c r="F29" t="n">
-        <v>8.463405847549438</v>
+        <v>8.44550633430481</v>
       </c>
       <c r="G29" t="n">
-        <v>9.100304365158081</v>
+        <v>10.71418857574463</v>
       </c>
       <c r="H29" t="n">
-        <v>6.806665658950806</v>
+        <v>9.457900524139404</v>
       </c>
       <c r="I29" t="n">
-        <v>9.396146535873413</v>
+        <v>8.511784076690674</v>
       </c>
       <c r="J29" t="n">
-        <v>9.560153961181641</v>
+        <v>9.392069339752197</v>
       </c>
       <c r="K29" t="n">
-        <v>6.780727624893188</v>
+        <v>9.639413833618164</v>
       </c>
       <c r="L29" t="n">
-        <v>8.459255814552307</v>
+        <v>9.548561477661133</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>9.004528045654297</v>
+        <v>8.831476926803589</v>
       </c>
       <c r="C30" t="n">
-        <v>8.737720727920532</v>
+        <v>7.866454839706421</v>
       </c>
       <c r="D30" t="n">
-        <v>9.980069875717163</v>
+        <v>9.758609056472778</v>
       </c>
       <c r="E30" t="n">
-        <v>8.494837045669556</v>
+        <v>8.803587436676025</v>
       </c>
       <c r="F30" t="n">
-        <v>6.993199825286865</v>
+        <v>7.439024925231934</v>
       </c>
       <c r="G30" t="n">
-        <v>8.176649570465088</v>
+        <v>8.531768798828125</v>
       </c>
       <c r="H30" t="n">
-        <v>9.390072345733643</v>
+        <v>8.977200746536255</v>
       </c>
       <c r="I30" t="n">
-        <v>9.422993659973145</v>
+        <v>10.12269306182861</v>
       </c>
       <c r="J30" t="n">
-        <v>8.044480562210083</v>
+        <v>8.781125545501709</v>
       </c>
       <c r="K30" t="n">
-        <v>9.055441856384277</v>
+        <v>7.517446994781494</v>
       </c>
       <c r="L30" t="n">
-        <v>8.729999351501466</v>
+        <v>8.662938833236694</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>8.034516572952271</v>
+        <v>7.951223611831665</v>
       </c>
       <c r="C31" t="n">
-        <v>7.821092128753662</v>
+        <v>8.085869073867798</v>
       </c>
       <c r="D31" t="n">
-        <v>7.037065267562866</v>
+        <v>8.78710675239563</v>
       </c>
       <c r="E31" t="n">
-        <v>7.287923812866211</v>
+        <v>8.674400806427002</v>
       </c>
       <c r="F31" t="n">
-        <v>7.900351285934448</v>
+        <v>8.074391841888428</v>
       </c>
       <c r="G31" t="n">
-        <v>8.337258815765381</v>
+        <v>9.470375299453735</v>
       </c>
       <c r="H31" t="n">
-        <v>7.944821119308472</v>
+        <v>8.868422508239746</v>
       </c>
       <c r="I31" t="n">
-        <v>8.540254831314087</v>
+        <v>7.878389358520508</v>
       </c>
       <c r="J31" t="n">
-        <v>6.817306995391846</v>
+        <v>7.347806930541992</v>
       </c>
       <c r="K31" t="n">
-        <v>6.447744846343994</v>
+        <v>9.694799900054932</v>
       </c>
       <c r="L31" t="n">
-        <v>7.616833567619324</v>
+        <v>8.483278608322143</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>5.807899475097656</v>
+        <v>6.489999532699585</v>
       </c>
       <c r="C32" t="n">
-        <v>10.10320949554443</v>
+        <v>7.830017328262329</v>
       </c>
       <c r="D32" t="n">
-        <v>7.571821451187134</v>
+        <v>6.614157438278198</v>
       </c>
       <c r="E32" t="n">
-        <v>6.22679615020752</v>
+        <v>6.916866064071655</v>
       </c>
       <c r="F32" t="n">
-        <v>6.490626573562622</v>
+        <v>8.198978424072266</v>
       </c>
       <c r="G32" t="n">
-        <v>7.483025550842285</v>
+        <v>6.526516675949097</v>
       </c>
       <c r="H32" t="n">
-        <v>6.305428981781006</v>
+        <v>7.957782506942749</v>
       </c>
       <c r="I32" t="n">
-        <v>7.826039791107178</v>
+        <v>7.194552183151245</v>
       </c>
       <c r="J32" t="n">
-        <v>6.723416805267334</v>
+        <v>6.612823724746704</v>
       </c>
       <c r="K32" t="n">
-        <v>6.345842599868774</v>
+        <v>7.059132099151611</v>
       </c>
       <c r="L32" t="n">
-        <v>7.088410687446594</v>
+        <v>7.140082597732544</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>6.136218309402466</v>
+        <v>9.607979774475098</v>
       </c>
       <c r="C33" t="n">
-        <v>6.384955167770386</v>
+        <v>7.151910305023193</v>
       </c>
       <c r="D33" t="n">
-        <v>7.021105527877808</v>
+        <v>7.117019891738892</v>
       </c>
       <c r="E33" t="n">
-        <v>7.583161354064941</v>
+        <v>8.966150999069214</v>
       </c>
       <c r="F33" t="n">
-        <v>6.640607833862305</v>
+        <v>7.053138017654419</v>
       </c>
       <c r="G33" t="n">
-        <v>6.410703659057617</v>
+        <v>6.874146938323975</v>
       </c>
       <c r="H33" t="n">
-        <v>6.905908346176147</v>
+        <v>8.00217080116272</v>
       </c>
       <c r="I33" t="n">
-        <v>7.449047565460205</v>
+        <v>6.957896709442139</v>
       </c>
       <c r="J33" t="n">
-        <v>7.636535882949829</v>
+        <v>9.015974044799805</v>
       </c>
       <c r="K33" t="n">
-        <v>6.991196632385254</v>
+        <v>6.564783096313477</v>
       </c>
       <c r="L33" t="n">
-        <v>6.915944027900696</v>
+        <v>7.731117057800293</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>7.310867309570312</v>
+        <v>7.684937477111816</v>
       </c>
       <c r="C34" t="n">
-        <v>6.202212572097778</v>
+        <v>7.21658992767334</v>
       </c>
       <c r="D34" t="n">
-        <v>7.457018136978149</v>
+        <v>6.015665292739868</v>
       </c>
       <c r="E34" t="n">
-        <v>6.290494203567505</v>
+        <v>7.451008558273315</v>
       </c>
       <c r="F34" t="n">
-        <v>6.637226343154907</v>
+        <v>8.107855558395386</v>
       </c>
       <c r="G34" t="n">
-        <v>5.990409851074219</v>
+        <v>7.312855005264282</v>
       </c>
       <c r="H34" t="n">
-        <v>7.320448398590088</v>
+        <v>7.557721376419067</v>
       </c>
       <c r="I34" t="n">
-        <v>6.796355009078979</v>
+        <v>8.398088693618774</v>
       </c>
       <c r="J34" t="n">
-        <v>7.620156288146973</v>
+        <v>9.005115747451782</v>
       </c>
       <c r="K34" t="n">
-        <v>6.564412355422974</v>
+        <v>8.223186016082764</v>
       </c>
       <c r="L34" t="n">
-        <v>6.818960046768188</v>
+        <v>7.69730236530304</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>7.317463159561157</v>
+        <v>7.95879864692688</v>
       </c>
       <c r="C35" t="n">
-        <v>9.082862854003906</v>
+        <v>9.626506805419922</v>
       </c>
       <c r="D35" t="n">
-        <v>6.648703575134277</v>
+        <v>9.307751178741455</v>
       </c>
       <c r="E35" t="n">
-        <v>7.440650701522827</v>
+        <v>8.429562568664551</v>
       </c>
       <c r="F35" t="n">
-        <v>6.93617582321167</v>
+        <v>7.765690803527832</v>
       </c>
       <c r="G35" t="n">
-        <v>6.718424558639526</v>
+        <v>7.812089443206787</v>
       </c>
       <c r="H35" t="n">
-        <v>8.342232942581177</v>
+        <v>7.618561983108521</v>
       </c>
       <c r="I35" t="n">
-        <v>6.759306907653809</v>
+        <v>7.383196830749512</v>
       </c>
       <c r="J35" t="n">
-        <v>7.083578824996948</v>
+        <v>7.727838277816772</v>
       </c>
       <c r="K35" t="n">
-        <v>9.171642303466797</v>
+        <v>7.798197269439697</v>
       </c>
       <c r="L35" t="n">
-        <v>7.55010416507721</v>
+        <v>8.142819380760193</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>9.08734917640686</v>
+        <v>10.87177276611328</v>
       </c>
       <c r="C36" t="n">
-        <v>8.952739238739014</v>
+        <v>8.951677083969116</v>
       </c>
       <c r="D36" t="n">
-        <v>9.133785486221313</v>
+        <v>8.899687051773071</v>
       </c>
       <c r="E36" t="n">
-        <v>7.442644119262695</v>
+        <v>10.30865025520325</v>
       </c>
       <c r="F36" t="n">
-        <v>8.684915065765381</v>
+        <v>9.118283271789551</v>
       </c>
       <c r="G36" t="n">
-        <v>11.69653296470642</v>
+        <v>10.69715762138367</v>
       </c>
       <c r="H36" t="n">
-        <v>9.885783910751343</v>
+        <v>10.84776091575623</v>
       </c>
       <c r="I36" t="n">
-        <v>7.512943983078003</v>
+        <v>11.10776782035828</v>
       </c>
       <c r="J36" t="n">
-        <v>8.791645765304565</v>
+        <v>11.03990840911865</v>
       </c>
       <c r="K36" t="n">
-        <v>10.32918572425842</v>
+        <v>8.020611047744751</v>
       </c>
       <c r="L36" t="n">
-        <v>9.151752543449401</v>
+        <v>9.986327624320984</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>5.784783124923706</v>
+        <v>5.982228994369507</v>
       </c>
       <c r="C37" t="n">
-        <v>6.34681510925293</v>
+        <v>8.533286571502686</v>
       </c>
       <c r="D37" t="n">
-        <v>6.6657395362854</v>
+        <v>6.54679799079895</v>
       </c>
       <c r="E37" t="n">
-        <v>5.6910240650177</v>
+        <v>6.650040626525879</v>
       </c>
       <c r="F37" t="n">
-        <v>5.805202722549438</v>
+        <v>6.37576961517334</v>
       </c>
       <c r="G37" t="n">
-        <v>5.836117506027222</v>
+        <v>7.605611801147461</v>
       </c>
       <c r="H37" t="n">
-        <v>6.061087131500244</v>
+        <v>8.583588123321533</v>
       </c>
       <c r="I37" t="n">
-        <v>5.741890668869019</v>
+        <v>13.3349244594574</v>
       </c>
       <c r="J37" t="n">
-        <v>6.328384399414062</v>
+        <v>6.203199625015259</v>
       </c>
       <c r="K37" t="n">
-        <v>5.65259861946106</v>
+        <v>8.411559104919434</v>
       </c>
       <c r="L37" t="n">
-        <v>5.991364288330078</v>
+        <v>7.822700691223145</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>6.536849737167358</v>
+        <v>7.788175582885742</v>
       </c>
       <c r="C38" t="n">
-        <v>6.512924671173096</v>
+        <v>7.197675466537476</v>
       </c>
       <c r="D38" t="n">
-        <v>7.670444965362549</v>
+        <v>7.581671953201294</v>
       </c>
       <c r="E38" t="n">
-        <v>7.430095195770264</v>
+        <v>7.003635168075562</v>
       </c>
       <c r="F38" t="n">
-        <v>6.499944925308228</v>
+        <v>8.317301988601685</v>
       </c>
       <c r="G38" t="n">
-        <v>7.564725637435913</v>
+        <v>7.24205756187439</v>
       </c>
       <c r="H38" t="n">
-        <v>8.503854274749756</v>
+        <v>7.341778039932251</v>
       </c>
       <c r="I38" t="n">
-        <v>8.098341941833496</v>
+        <v>7.131333112716675</v>
       </c>
       <c r="J38" t="n">
-        <v>6.582218170166016</v>
+        <v>7.178720712661743</v>
       </c>
       <c r="K38" t="n">
-        <v>6.69675087928772</v>
+        <v>7.312859058380127</v>
       </c>
       <c r="L38" t="n">
-        <v>7.209615039825439</v>
+        <v>7.409520864486694</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>6.758305788040161</v>
+        <v>6.293457746505737</v>
       </c>
       <c r="C39" t="n">
-        <v>7.733789920806885</v>
+        <v>7.115380764007568</v>
       </c>
       <c r="D39" t="n">
-        <v>5.875615358352661</v>
+        <v>6.592678785324097</v>
       </c>
       <c r="E39" t="n">
-        <v>6.297098875045776</v>
+        <v>6.904890775680542</v>
       </c>
       <c r="F39" t="n">
-        <v>8.904841184616089</v>
+        <v>7.720814943313599</v>
       </c>
       <c r="G39" t="n">
-        <v>7.037097454071045</v>
+        <v>6.565269231796265</v>
       </c>
       <c r="H39" t="n">
-        <v>6.321487188339233</v>
+        <v>7.080969333648682</v>
       </c>
       <c r="I39" t="n">
-        <v>6.020663976669312</v>
+        <v>6.976227521896362</v>
       </c>
       <c r="J39" t="n">
-        <v>5.732890605926514</v>
+        <v>6.78685474395752</v>
       </c>
       <c r="K39" t="n">
-        <v>5.745380163192749</v>
+        <v>7.164063453674316</v>
       </c>
       <c r="L39" t="n">
-        <v>6.642717051506042</v>
+        <v>6.920060729980468</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>8.328279972076416</v>
+        <v>7.301921129226685</v>
       </c>
       <c r="C40" t="n">
-        <v>6.310448408126831</v>
+        <v>10.07281351089478</v>
       </c>
       <c r="D40" t="n">
-        <v>6.348332405090332</v>
+        <v>7.454981565475464</v>
       </c>
       <c r="E40" t="n">
-        <v>6.742868661880493</v>
+        <v>7.396163940429688</v>
       </c>
       <c r="F40" t="n">
-        <v>6.476500749588013</v>
+        <v>7.531310319900513</v>
       </c>
       <c r="G40" t="n">
-        <v>7.390176773071289</v>
+        <v>9.445919275283813</v>
       </c>
       <c r="H40" t="n">
-        <v>6.825644016265869</v>
+        <v>7.286939144134521</v>
       </c>
       <c r="I40" t="n">
-        <v>7.422107219696045</v>
+        <v>6.694444894790649</v>
       </c>
       <c r="J40" t="n">
-        <v>8.570674180984497</v>
+        <v>7.358726263046265</v>
       </c>
       <c r="K40" t="n">
-        <v>7.876441478729248</v>
+        <v>6.897929906845093</v>
       </c>
       <c r="L40" t="n">
-        <v>7.229147386550903</v>
+        <v>7.744114995002747</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>9.087368011474609</v>
+        <v>9.940666675567627</v>
       </c>
       <c r="C41" t="n">
-        <v>8.987144470214844</v>
+        <v>10.51518988609314</v>
       </c>
       <c r="D41" t="n">
-        <v>8.56269383430481</v>
+        <v>10.67528581619263</v>
       </c>
       <c r="E41" t="n">
-        <v>7.03706955909729</v>
+        <v>9.101306676864624</v>
       </c>
       <c r="F41" t="n">
-        <v>9.898291826248169</v>
+        <v>8.227557897567749</v>
       </c>
       <c r="G41" t="n">
-        <v>7.491414546966553</v>
+        <v>8.537752866744995</v>
       </c>
       <c r="H41" t="n">
-        <v>9.751682996749878</v>
+        <v>9.693785905838013</v>
       </c>
       <c r="I41" t="n">
-        <v>10.53565168380737</v>
+        <v>8.145731687545776</v>
       </c>
       <c r="J41" t="n">
-        <v>10.28931045532227</v>
+        <v>7.540315866470337</v>
       </c>
       <c r="K41" t="n">
-        <v>8.74820351600647</v>
+        <v>10.52165508270264</v>
       </c>
       <c r="L41" t="n">
-        <v>9.038883090019226</v>
+        <v>9.289924836158752</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>5.494501113891602</v>
+        <v>7.907328844070435</v>
       </c>
       <c r="C42" t="n">
-        <v>7.016129016876221</v>
+        <v>6.66551947593689</v>
       </c>
       <c r="D42" t="n">
-        <v>7.387212991714478</v>
+        <v>5.886056900024414</v>
       </c>
       <c r="E42" t="n">
-        <v>6.635083675384521</v>
+        <v>8.161205768585205</v>
       </c>
       <c r="F42" t="n">
-        <v>5.387759923934937</v>
+        <v>7.577820062637329</v>
       </c>
       <c r="G42" t="n">
-        <v>7.481361389160156</v>
+        <v>9.490781545639038</v>
       </c>
       <c r="H42" t="n">
-        <v>5.493269443511963</v>
+        <v>5.92606520652771</v>
       </c>
       <c r="I42" t="n">
-        <v>5.954009056091309</v>
+        <v>8.172467708587646</v>
       </c>
       <c r="J42" t="n">
-        <v>5.713659048080444</v>
+        <v>7.09490966796875</v>
       </c>
       <c r="K42" t="n">
-        <v>7.365858316421509</v>
+        <v>7.718844413757324</v>
       </c>
       <c r="L42" t="n">
-        <v>6.392884397506714</v>
+        <v>7.460099959373474</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>6.166448593139648</v>
+        <v>7.433062553405762</v>
       </c>
       <c r="C43" t="n">
-        <v>7.439120292663574</v>
+        <v>7.825034141540527</v>
       </c>
       <c r="D43" t="n">
-        <v>5.819872140884399</v>
+        <v>6.320395946502686</v>
       </c>
       <c r="E43" t="n">
-        <v>6.390897989273071</v>
+        <v>7.008246898651123</v>
       </c>
       <c r="F43" t="n">
-        <v>7.442150831222534</v>
+        <v>7.995217800140381</v>
       </c>
       <c r="G43" t="n">
-        <v>5.880696296691895</v>
+        <v>6.689593553543091</v>
       </c>
       <c r="H43" t="n">
-        <v>6.063470363616943</v>
+        <v>7.410690546035767</v>
       </c>
       <c r="I43" t="n">
-        <v>6.292155981063843</v>
+        <v>6.157972574234009</v>
       </c>
       <c r="J43" t="n">
-        <v>7.566811323165894</v>
+        <v>6.995784759521484</v>
       </c>
       <c r="K43" t="n">
-        <v>6.849230289459229</v>
+        <v>6.400823593139648</v>
       </c>
       <c r="L43" t="n">
-        <v>6.591085410118103</v>
+        <v>7.023682236671448</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>6.65369176864624</v>
+        <v>10.59195351600647</v>
       </c>
       <c r="C44" t="n">
-        <v>6.609815359115601</v>
+        <v>7.261643409729004</v>
       </c>
       <c r="D44" t="n">
-        <v>6.444221019744873</v>
+        <v>7.131946325302124</v>
       </c>
       <c r="E44" t="n">
-        <v>7.206253051757812</v>
+        <v>6.802292585372925</v>
       </c>
       <c r="F44" t="n">
-        <v>6.818289756774902</v>
+        <v>8.093429088592529</v>
       </c>
       <c r="G44" t="n">
-        <v>9.271378755569458</v>
+        <v>9.82142186164856</v>
       </c>
       <c r="H44" t="n">
-        <v>6.679623126983643</v>
+        <v>6.88507080078125</v>
       </c>
       <c r="I44" t="n">
-        <v>7.186295509338379</v>
+        <v>6.895555734634399</v>
       </c>
       <c r="J44" t="n">
-        <v>6.616798400878906</v>
+        <v>8.543277025222778</v>
       </c>
       <c r="K44" t="n">
-        <v>6.477659940719604</v>
+        <v>7.315448760986328</v>
       </c>
       <c r="L44" t="n">
-        <v>6.996402668952942</v>
+        <v>7.934203910827637</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>8.218596696853638</v>
+        <v>8.482349395751953</v>
       </c>
       <c r="C45" t="n">
-        <v>7.68948769569397</v>
+        <v>6.930818796157837</v>
       </c>
       <c r="D45" t="n">
-        <v>6.924867868423462</v>
+        <v>8.664462327957153</v>
       </c>
       <c r="E45" t="n">
-        <v>6.994173288345337</v>
+        <v>8.87938404083252</v>
       </c>
       <c r="F45" t="n">
-        <v>7.022107124328613</v>
+        <v>6.827094793319702</v>
       </c>
       <c r="G45" t="n">
-        <v>7.658988237380981</v>
+        <v>9.811556816101074</v>
       </c>
       <c r="H45" t="n">
-        <v>8.037517070770264</v>
+        <v>7.371228694915771</v>
       </c>
       <c r="I45" t="n">
-        <v>8.177650213241577</v>
+        <v>7.656481027603149</v>
       </c>
       <c r="J45" t="n">
-        <v>8.426051378250122</v>
+        <v>7.343264579772949</v>
       </c>
       <c r="K45" t="n">
-        <v>9.067916393280029</v>
+        <v>9.582043647766113</v>
       </c>
       <c r="L45" t="n">
-        <v>7.821735596656799</v>
+        <v>8.154868412017823</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>6.733396768569946</v>
+        <v>7.182691812515259</v>
       </c>
       <c r="C46" t="n">
-        <v>6.903936147689819</v>
+        <v>6.957773208618164</v>
       </c>
       <c r="D46" t="n">
-        <v>7.521375179290771</v>
+        <v>7.141817569732666</v>
       </c>
       <c r="E46" t="n">
-        <v>5.999729871749878</v>
+        <v>7.023102283477783</v>
       </c>
       <c r="F46" t="n">
-        <v>7.618586540222168</v>
+        <v>7.589156627655029</v>
       </c>
       <c r="G46" t="n">
-        <v>7.324832916259766</v>
+        <v>8.643487930297852</v>
       </c>
       <c r="H46" t="n">
-        <v>6.919882535934448</v>
+        <v>7.219572305679321</v>
       </c>
       <c r="I46" t="n">
-        <v>7.423096418380737</v>
+        <v>9.66034197807312</v>
       </c>
       <c r="J46" t="n">
-        <v>8.722301959991455</v>
+        <v>7.416130065917969</v>
       </c>
       <c r="K46" t="n">
-        <v>8.09888768196106</v>
+        <v>8.028555870056152</v>
       </c>
       <c r="L46" t="n">
-        <v>7.326602602005005</v>
+        <v>7.686262965202332</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>6.973256587982178</v>
+        <v>9.862985849380493</v>
       </c>
       <c r="C47" t="n">
-        <v>6.983696699142456</v>
+        <v>10.16361117362976</v>
       </c>
       <c r="D47" t="n">
-        <v>10.34274744987488</v>
+        <v>10.41361832618713</v>
       </c>
       <c r="E47" t="n">
-        <v>8.440475463867188</v>
+        <v>8.455452919006348</v>
       </c>
       <c r="F47" t="n">
-        <v>6.959765195846558</v>
+        <v>9.314763784408569</v>
       </c>
       <c r="G47" t="n">
-        <v>8.967175722122192</v>
+        <v>8.619043111801147</v>
       </c>
       <c r="H47" t="n">
-        <v>6.847589731216431</v>
+        <v>8.128771305084229</v>
       </c>
       <c r="I47" t="n">
-        <v>9.148199319839478</v>
+        <v>9.562648296356201</v>
       </c>
       <c r="J47" t="n">
-        <v>7.18768835067749</v>
+        <v>8.804553508758545</v>
       </c>
       <c r="K47" t="n">
-        <v>8.114816188812256</v>
+        <v>8.315311193466187</v>
       </c>
       <c r="L47" t="n">
-        <v>7.99654107093811</v>
+        <v>9.164075946807861</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>8.515860795974731</v>
+        <v>7.792108297348022</v>
       </c>
       <c r="C48" t="n">
-        <v>6.79070782661438</v>
+        <v>9.082868576049805</v>
       </c>
       <c r="D48" t="n">
-        <v>6.485966920852661</v>
+        <v>7.088452577590942</v>
       </c>
       <c r="E48" t="n">
-        <v>6.129863262176514</v>
+        <v>8.676403522491455</v>
       </c>
       <c r="F48" t="n">
-        <v>6.211191892623901</v>
+        <v>7.611598491668701</v>
       </c>
       <c r="G48" t="n">
-        <v>7.05703592300415</v>
+        <v>6.797166109085083</v>
       </c>
       <c r="H48" t="n">
-        <v>6.660552501678467</v>
+        <v>6.978199481964111</v>
       </c>
       <c r="I48" t="n">
-        <v>7.66546630859375</v>
+        <v>7.007127523422241</v>
       </c>
       <c r="J48" t="n">
-        <v>8.501900672912598</v>
+        <v>9.261404037475586</v>
       </c>
       <c r="K48" t="n">
-        <v>7.251516819000244</v>
+        <v>7.534785747528076</v>
       </c>
       <c r="L48" t="n">
-        <v>7.12700629234314</v>
+        <v>7.783011436462402</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>7.094439744949341</v>
+        <v>8.339776277542114</v>
       </c>
       <c r="C49" t="n">
-        <v>6.951772689819336</v>
+        <v>8.235004425048828</v>
       </c>
       <c r="D49" t="n">
-        <v>8.86296558380127</v>
+        <v>7.777686357498169</v>
       </c>
       <c r="E49" t="n">
-        <v>7.877946376800537</v>
+        <v>9.734706401824951</v>
       </c>
       <c r="F49" t="n">
-        <v>6.912887334823608</v>
+        <v>7.94475269317627</v>
       </c>
       <c r="G49" t="n">
-        <v>6.985213994979858</v>
+        <v>8.188706398010254</v>
       </c>
       <c r="H49" t="n">
-        <v>7.642529010772705</v>
+        <v>8.310359954833984</v>
       </c>
       <c r="I49" t="n">
-        <v>7.805077314376831</v>
+        <v>9.54070258140564</v>
       </c>
       <c r="J49" t="n">
-        <v>7.234593391418457</v>
+        <v>8.698797941207886</v>
       </c>
       <c r="K49" t="n">
-        <v>7.634544610977173</v>
+        <v>8.714296102523804</v>
       </c>
       <c r="L49" t="n">
-        <v>7.500197005271912</v>
+        <v>8.548478913307189</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>10.00302028656006</v>
+        <v>10.22844266891479</v>
       </c>
       <c r="C50" t="n">
-        <v>8.042826414108276</v>
+        <v>7.166228771209717</v>
       </c>
       <c r="D50" t="n">
-        <v>6.987670421600342</v>
+        <v>7.444028854370117</v>
       </c>
       <c r="E50" t="n">
-        <v>7.666956186294556</v>
+        <v>8.21708083152771</v>
       </c>
       <c r="F50" t="n">
-        <v>7.729795217514038</v>
+        <v>8.963151931762695</v>
       </c>
       <c r="G50" t="n">
-        <v>8.368197441101074</v>
+        <v>7.637506246566772</v>
       </c>
       <c r="H50" t="n">
-        <v>9.026016712188721</v>
+        <v>7.51336145401001</v>
       </c>
       <c r="I50" t="n">
-        <v>9.309782028198242</v>
+        <v>10.14387202262878</v>
       </c>
       <c r="J50" t="n">
-        <v>8.774637222290039</v>
+        <v>9.3990318775177</v>
       </c>
       <c r="K50" t="n">
-        <v>7.198656797409058</v>
+        <v>9.61152172088623</v>
       </c>
       <c r="L50" t="n">
-        <v>8.310755872726441</v>
+        <v>8.632422637939452</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>6.958776235580444</v>
+        <v>7.621732711791992</v>
       </c>
       <c r="C51" t="n">
-        <v>8.313334941864014</v>
+        <v>8.7482008934021</v>
       </c>
       <c r="D51" t="n">
-        <v>7.553232431411743</v>
+        <v>8.765662431716919</v>
       </c>
       <c r="E51" t="n">
-        <v>7.02059531211853</v>
+        <v>7.134311199188232</v>
       </c>
       <c r="F51" t="n">
-        <v>7.686977624893188</v>
+        <v>7.30189847946167</v>
       </c>
       <c r="G51" t="n">
-        <v>6.973886013031006</v>
+        <v>8.380118608474731</v>
       </c>
       <c r="H51" t="n">
-        <v>7.196950674057007</v>
+        <v>7.01510763168335</v>
       </c>
       <c r="I51" t="n">
-        <v>7.323829412460327</v>
+        <v>7.934273242950439</v>
       </c>
       <c r="J51" t="n">
-        <v>6.101955652236938</v>
+        <v>7.575716018676758</v>
       </c>
       <c r="K51" t="n">
-        <v>6.651075839996338</v>
+        <v>6.587198257446289</v>
       </c>
       <c r="L51" t="n">
-        <v>7.178061413764953</v>
+        <v>7.706421947479248</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>7.344954376220703</v>
+        <v>8.237285590171814</v>
       </c>
       <c r="C52" t="n">
-        <v>7.432490487098693</v>
+        <v>8.137025580406188</v>
       </c>
       <c r="D52" t="n">
-        <v>7.337415370941162</v>
+        <v>7.9907546043396</v>
       </c>
       <c r="E52" t="n">
-        <v>7.372597432136535</v>
+        <v>8.055110793113709</v>
       </c>
       <c r="F52" t="n">
-        <v>7.414861135482788</v>
+        <v>7.899979376792908</v>
       </c>
       <c r="G52" t="n">
-        <v>7.508366379737854</v>
+        <v>8.22231086730957</v>
       </c>
       <c r="H52" t="n">
-        <v>7.529693622589111</v>
+        <v>7.891687173843383</v>
       </c>
       <c r="I52" t="n">
-        <v>7.615228948593139</v>
+        <v>8.314797115325927</v>
       </c>
       <c r="J52" t="n">
-        <v>7.319106583595276</v>
+        <v>8.122533020973206</v>
       </c>
       <c r="K52" t="n">
-        <v>7.539174127578735</v>
+        <v>8.230405173301698</v>
       </c>
       <c r="L52" t="n">
-        <v>7.441388846397399</v>
+        <v>8.1101889295578</v>
       </c>
     </row>
   </sheetData>
